--- a/business-libraries/test-data/class_system/attribution.xlsx
+++ b/business-libraries/test-data/class_system/attribution.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="⑤b 归因-计算变量" sheetId="1" r:id="rId1"/>
-    <sheet name="⑤c 归因-分级规则" sheetId="2" r:id="rId2"/>
-    <sheet name="⑥ 归因-红线熔断" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤c 归因项" sheetId="2" r:id="rId2"/>
+    <sheet name="⑤d 证据规则" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤e 分级规则" sheetId="4" r:id="rId4"/>
+    <sheet name="⑥ 归因-红线熔断" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,19 +428,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>总负荷指数</v>
+        <v>系统均分</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>总分</v>
+        <v>均分</v>
       </c>
       <c r="D2" t="str">
-        <v>五题得分总和</v>
+        <v>五系统整体均分，越高表示越薄弱</v>
       </c>
       <c r="E2" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -447,367 +449,805 @@
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>情绪耗竭指数</v>
-      </c>
-      <c r="B3" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C3" t="str">
-        <v>维度[EMOTION]</v>
-      </c>
-      <c r="D3" t="str">
-        <v>情绪状态维度均值</v>
-      </c>
-      <c r="E3" t="str">
-        <v>C_FIVE_Q</v>
-      </c>
-      <c r="F3" t="str">
-        <v>q1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>EMOTION</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>连续低意义感次数</v>
-      </c>
-      <c r="B4" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C4" t="str">
-        <v>COUNT_CONSECUTIVE(题[q3] &lt;= 2, 4)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>统计最近连续4次评估中意义感知得分&lt;=2的次数</v>
-      </c>
-      <c r="E4" t="str">
-        <v>C_FIVE_Q</v>
-      </c>
-      <c r="F4" t="str">
-        <v>q3</v>
-      </c>
-      <c r="G4" t="str">
-        <v>MEANING</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>规则编码*</v>
+        <v>归因编码*</v>
       </c>
       <c r="B1" t="str">
+        <v>归因名称*</v>
+      </c>
+      <c r="C1" t="str">
         <v>所属模块*</v>
       </c>
-      <c r="C1" t="str">
-        <v>依据量表编码*</v>
-      </c>
       <c r="D1" t="str">
-        <v>优先级*</v>
+        <v>权重基数*</v>
       </c>
       <c r="E1" t="str">
-        <v>触发条件</v>
+        <v>工具标签*</v>
       </c>
       <c r="F1" t="str">
-        <v>命中等级*</v>
+        <v>归因说明</v>
       </c>
       <c r="G1" t="str">
-        <v>等级中文名*</v>
+        <v>高分表现</v>
       </c>
       <c r="H1" t="str">
-        <v>是否红线熔断*</v>
+        <v>典型诱因</v>
       </c>
       <c r="I1" t="str">
-        <v>主归因*</v>
+        <v>建议动作</v>
       </c>
       <c r="J1" t="str">
-        <v>次归因</v>
-      </c>
-      <c r="K1" t="str">
-        <v>归因理由*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>工具标签*</v>
-      </c>
-      <c r="M1" t="str">
-        <v>结果说明*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>输出动作摘要</v>
-      </c>
-      <c r="O1" t="str">
-        <v>输出工具摘要</v>
-      </c>
-      <c r="P1" t="str">
-        <v>升级条件</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>升级目标</v>
-      </c>
-      <c r="R1" t="str">
-        <v>复评触发条件</v>
-      </c>
-      <c r="S1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C-RED-Q1-Q3</v>
+        <v>CS_AT_GOAL</v>
       </c>
       <c r="B2" t="str">
+        <v>目标系统未落地</v>
+      </c>
+      <c r="C2" t="str">
         <v>class_system</v>
       </c>
-      <c r="C2" t="str">
-        <v>C_FIVE_Q</v>
-      </c>
       <c r="D2" t="str">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>class_system,goal</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>班级目标没有被学生理解，或没有转化为可观察的阶段性成果。</v>
       </c>
       <c r="G2" t="str">
-        <v>需立即关注</v>
+        <v>学生说不出班级目标；目标只贴在墙上</v>
       </c>
       <c r="H2" t="str">
-        <v>是</v>
+        <v>目标由教师单方面制定且缺少里程碑拆解</v>
       </c>
       <c r="I2" t="str">
-        <v>纪律与凝聚力双低</v>
+        <v>把本学期目标拆成三个可观察的里程碑，与学生共同确认第一个</v>
       </c>
       <c r="J2" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Q1疲劳&gt;=4分且Q3意义感&lt;=2分，两者同时处于高危水平，教师可能正经历情绪耗竭的核心阶段</v>
-      </c>
-      <c r="L2" t="str">
-        <v>class_system,orange,discipline</v>
-      </c>
-      <c r="M2" t="str">
-        <v>纪律与凝聚力双低风险同时处于高位，已暂停常规建议并转介。</v>
-      </c>
-      <c r="N2" t="str">
-        <v>建议安排心理专员面谈，暂缓常规班级评估</v>
-      </c>
-      <c r="O2" t="str">
-        <v>班会引导框架（应急）、情绪温度计自评</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>下次评估Q1或Q3任一&gt;=3分时触发复评</v>
-      </c>
-      <c r="S2" t="str">
-        <v>PRD 8.2.1</v>
+        <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C-ORANGE</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="B3" t="str">
+        <v>组织系统缺位</v>
+      </c>
+      <c r="C3" t="str">
         <v>class_system</v>
       </c>
-      <c r="C3" t="str">
-        <v>C_FIVE_Q</v>
-      </c>
       <c r="D3" t="str">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 17</v>
+        <v>class_system,org</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>班级事务过度集中在教师身上，学生岗位职责不清或无法稳定运转。</v>
       </c>
       <c r="G3" t="str">
-        <v>需关注</v>
+        <v>所有事都要教师亲自过问；班干部形同虚设</v>
       </c>
       <c r="H3" t="str">
-        <v>否</v>
+        <v>岗位设置缺少职责说明和交接流程</v>
       </c>
       <c r="I3" t="str">
-        <v>班级氛围偏低</v>
+        <v>选一个日常事务，写清责任人、执行步骤、异常处理和复盘时间，试行一周</v>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>总分&gt;=17分，教师在多个维度上感受到压力，但未达到红线阈值</v>
-      </c>
-      <c r="L3" t="str">
-        <v>class_system,yellow,motivation</v>
-      </c>
-      <c r="M3" t="str">
-        <v>您的整体状态在多个维度上偏高，建议重点关注并选择1-2项工具开始调整。</v>
-      </c>
-      <c r="N3" t="str">
-        <v>建议本月内完成一次深度自评</v>
-      </c>
-      <c r="O3" t="str">
-        <v>小组积分制、冲突调解话术</v>
-      </c>
-      <c r="P3" t="str">
-        <v>连续3次评估仍为orange</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>升级至red评估流程</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v>PRD 8.2.1</v>
+        <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>C-YELLOW</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="B4" t="str">
+        <v>活动系统空转</v>
+      </c>
+      <c r="C4" t="str">
         <v>class_system</v>
       </c>
-      <c r="C4" t="str">
-        <v>C_FIVE_Q</v>
-      </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>维度[EMOTION] &gt;= 3.5</v>
+        <v>class_system,activity</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>班级活动没有回应学生真实需要，或缺少复盘导致无法沉淀。</v>
       </c>
       <c r="G4" t="str">
-        <v>需留意</v>
+        <v>活动办完就结束，学生参与度低</v>
       </c>
       <c r="H4" t="str">
-        <v>否</v>
+        <v>活动主题由教师指定且无复盘环节</v>
       </c>
       <c r="I4" t="str">
-        <v>学生参与度不足</v>
+        <v>在下一次活动后加一个十分钟复盘，让学生说出一个保留动作和一个调整动作</v>
       </c>
       <c r="J4" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K4" t="str">
-        <v>情绪耗竭维度得分偏高，可能出现轻度职业倦怠的早期信号</v>
-      </c>
-      <c r="L4" t="str">
-        <v>class_system,orange,conflict</v>
-      </c>
-      <c r="M4" t="str">
-        <v>您的情绪耗竭维度偏高，建议开始关注自我照顾。</v>
-      </c>
-      <c r="N4" t="str">
-        <v>建议使用自我照顾工具</v>
-      </c>
-      <c r="O4" t="str">
-        <v>小组积分制、同伴支持圈</v>
-      </c>
-      <c r="P4" t="str">
-        <v>连续2次评估仍为yellow</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>升级至orange评估流程</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v>PRD 8.2.1</v>
+        <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>C-GREEN</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="B5" t="str">
+        <v>环境系统薄弱</v>
+      </c>
+      <c r="C5" t="str">
         <v>class_system</v>
       </c>
-      <c r="C5" t="str">
-        <v>C_FIVE_Q</v>
-      </c>
       <c r="D5" t="str">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>class_system,environment</v>
       </c>
       <c r="F5" t="str">
-        <v>green</v>
+        <v>班级规则和空间布置无法支撑稳定的学习秩序。</v>
       </c>
       <c r="G5" t="str">
-        <v>状态良好</v>
+        <v>规则只贴在墙上；混乱后难以恢复</v>
       </c>
       <c r="H5" t="str">
-        <v>否</v>
+        <v>规则由教师单方制定，缺少共同理解</v>
       </c>
       <c r="I5" t="str">
-        <v>状态稳定</v>
+        <v>挑一条最常被违反的规则，和学生一起重新表述成可观察的行为标准</v>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>当前评估未触发任何风险规则，教师整体状态稳定</v>
-      </c>
-      <c r="L5" t="str">
-        <v>class_system,green</v>
-      </c>
-      <c r="M5" t="str">
-        <v>当前状态整体稳定，保持现有节奏即可。</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v>PRD 8.2.1</v>
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CS_AT_RELATION</v>
+      </c>
+      <c r="B6" t="str">
+        <v>关系系统受损</v>
+      </c>
+      <c r="C6" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E6" t="str">
+        <v>class_system,relation</v>
+      </c>
+      <c r="F6" t="str">
+        <v>学生之间的冲突难以修复，缺少稳定的同伴支持结构。</v>
+      </c>
+      <c r="G6" t="str">
+        <v>冲突反复发生；存在被孤立的学生</v>
+      </c>
+      <c r="H6" t="str">
+        <v>缺少冲突处理流程和同伴互助机制</v>
+      </c>
+      <c r="I6" t="str">
+        <v>建立一个固定的冲突修复流程，并在下一次冲突时完整走一遍</v>
+      </c>
+      <c r="J6" t="str">
+        <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>证据编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>触发条件*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>证据权重*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>证据说明*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CS_EV_01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>CS_AT_GOAL</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D2" t="str">
+        <v>维度[CS_GOAL] &gt;= 4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="str">
+        <v>目标系统得分处于高位，目标未被学生理解或未落地</v>
+      </c>
+      <c r="G2" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CS_EV_02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>CS_AT_GOAL</v>
+      </c>
+      <c r="C3" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D3" t="str">
+        <v>维度[CS_GOAL] &gt;= 3</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>目标系统存在待建设的环节</v>
+      </c>
+      <c r="G3" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CS_EV_03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CS_AT_ORG</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D4" t="str">
+        <v>维度[CS_ORG] &gt;= 4</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F4" t="str">
+        <v>组织系统得分处于高位，事务过度集中在教师身上</v>
+      </c>
+      <c r="G4" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CS_EV_04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CS_AT_ORG</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D5" t="str">
+        <v>维度[CS_ORG] &gt;= 3</v>
+      </c>
+      <c r="E5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>组织系统存在待建设的环节</v>
+      </c>
+      <c r="G5" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CS_EV_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CS_AT_ACTIVITY</v>
+      </c>
+      <c r="C6" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D6" t="str">
+        <v>维度[CS_ACTIVITY] &gt;= 4</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F6" t="str">
+        <v>活动系统得分处于高位，活动缺少回应与复盘</v>
+      </c>
+      <c r="G6" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CS_EV_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>CS_AT_ACTIVITY</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D7" t="str">
+        <v>维度[CS_ACTIVITY] &gt;= 3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>活动系统存在待建设的环节</v>
+      </c>
+      <c r="G7" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_EV_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>CS_AT_ENV</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D8" t="str">
+        <v>维度[CS_ENV] &gt;= 4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F8" t="str">
+        <v>环境系统得分处于高位，秩序难以自主恢复</v>
+      </c>
+      <c r="G8" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_EV_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>CS_AT_ENV</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D9" t="str">
+        <v>维度[CS_ENV] &gt;= 3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>环境系统存在待建设的环节</v>
+      </c>
+      <c r="G9" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_EV_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>CS_AT_RELATION</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>维度[CS_RELATION] &gt;= 4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>3</v>
+      </c>
+      <c r="F10" t="str">
+        <v>关系系统得分处于高位，冲突难以修复</v>
+      </c>
+      <c r="G10" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_EV_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>CS_AT_RELATION</v>
+      </c>
+      <c r="C11" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D11" t="str">
+        <v>维度[CS_RELATION] &gt;= 3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>关系系统存在待建设的环节</v>
+      </c>
+      <c r="G11" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_EV_21</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CS_AT_ENV</v>
+      </c>
+      <c r="C12" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="D12" t="str">
+        <v>维度[CS_ORDER] &gt;= 3.5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>能量场问卷显示秩序需要教师持续在场维持</v>
+      </c>
+      <c r="G12" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_EV_22</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CS_AT_ORG</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="D13" t="str">
+        <v>维度[CS_ORDER] &gt;= 3</v>
+      </c>
+      <c r="E13" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>秩序对教师在场的依赖提示组织系统缺位</v>
+      </c>
+      <c r="G13" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_EV_23</v>
+      </c>
+      <c r="B14" t="str">
+        <v>CS_AT_RELATION</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="D14" t="str">
+        <v>维度[CS_CONNECT] &gt;= 3.5</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F14" t="str">
+        <v>能量场问卷显示学生之间缺少正向联结</v>
+      </c>
+      <c r="G14" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_EV_24</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CS_AT_ACTIVITY</v>
+      </c>
+      <c r="C15" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="D15" t="str">
+        <v>维度[CS_LEARNING] &gt;= 3.5</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2</v>
+      </c>
+      <c r="F15" t="str">
+        <v>学习投入依赖外部推动，活动未能激发内驱</v>
+      </c>
+      <c r="G15" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>规则编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>所属模块*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码</v>
+      </c>
+      <c r="D1" t="str">
+        <v>优先级*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="F1" t="str">
+        <v>命中等级*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>等级中文名*</v>
+      </c>
+      <c r="H1" t="str">
+        <v>严重度*</v>
+      </c>
+      <c r="I1" t="str">
+        <v>是否红线熔断*</v>
+      </c>
+      <c r="J1" t="str">
+        <v>结果说明*</v>
+      </c>
+      <c r="K1" t="str">
+        <v>升级条件</v>
+      </c>
+      <c r="L1" t="str">
+        <v>升级目标</v>
+      </c>
+      <c r="M1" t="str">
+        <v>复评触发条件</v>
+      </c>
+      <c r="N1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CS_GRADE_SURVIVAL</v>
+      </c>
+      <c r="B2" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10</v>
+      </c>
+      <c r="E2" t="str">
+        <v>系统均分 &gt;= 4</v>
+      </c>
+      <c r="F2" t="str">
+        <v>survival</v>
+      </c>
+      <c r="G2" t="str">
+        <v>生存期</v>
+      </c>
+      <c r="H2" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="I2" t="str">
+        <v>否</v>
+      </c>
+      <c r="J2" t="str">
+        <v>班级多个子系统同时薄弱，当前处于生存期，需要先稳住秩序再谈建设。</v>
+      </c>
+      <c r="K2" t="str">
+        <v>连续两次生存期</v>
+      </c>
+      <c r="L2" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M2" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N2" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CS_GRADE_NORMING</v>
+      </c>
+      <c r="B3" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C3" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D3" t="str">
+        <v>20</v>
+      </c>
+      <c r="E3" t="str">
+        <v>系统均分 &gt;= 3.2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>norming</v>
+      </c>
+      <c r="G3" t="str">
+        <v>规范期</v>
+      </c>
+      <c r="H3" t="str">
+        <v>high</v>
+      </c>
+      <c r="I3" t="str">
+        <v>否</v>
+      </c>
+      <c r="J3" t="str">
+        <v>班级处于规范期，重点是把薄弱系统补成可重复执行的机制。</v>
+      </c>
+      <c r="K3" t="str">
+        <v>连续两次规范期</v>
+      </c>
+      <c r="L3" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M3" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N3" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CS_GRADE_OPERATING</v>
+      </c>
+      <c r="B4" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CS_FIVE_SYS</v>
+      </c>
+      <c r="D4" t="str">
+        <v>30</v>
+      </c>
+      <c r="E4" t="str">
+        <v>系统均分 &gt;= 2.4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>operating</v>
+      </c>
+      <c r="G4" t="str">
+        <v>运行期</v>
+      </c>
+      <c r="H4" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I4" t="str">
+        <v>否</v>
+      </c>
+      <c r="J4" t="str">
+        <v>班级基本能够自主运行，可以聚焦单个子系统做精细建设。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>复评退回规范期或生存期</v>
+      </c>
+      <c r="L4" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M4" t="str">
+        <v>60天后复评</v>
+      </c>
+      <c r="N4" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CS_GRADE_MATURE</v>
+      </c>
+      <c r="B5" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>999</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>mature</v>
+      </c>
+      <c r="G5" t="str">
+        <v>成熟期</v>
+      </c>
+      <c r="H5" t="str">
+        <v>low</v>
+      </c>
+      <c r="I5" t="str">
+        <v>否</v>
+      </c>
+      <c r="J5" t="str">
+        <v>班级系统运行成熟，建议把已有经验沉淀成可交接的班级手册。</v>
+      </c>
+      <c r="K5" t="str">
+        <v>复评退回运行期以下</v>
+      </c>
+      <c r="L5" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M5" t="str">
+        <v>90天后复评</v>
+      </c>
+      <c r="N5" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
@@ -847,31 +1287,31 @@
         <v>class_system</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>维度[CS_RELATION] &gt;= 4.7</v>
       </c>
       <c r="C2" t="str">
-        <v>纪律与凝聚力双低，属班级系统建设模块红线</v>
+        <v>关系系统极端薄弱，可能存在校园欺凌或严重孤立</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
+        <v>暂停常规班级建设建议，转入学生个体问题模块做逐个筛查，并通知年级组长</v>
       </c>
       <c r="F2" t="str">
-        <v>1. 停止当前评估流程 2. 展示危机求助指引 3. 自动创建安全事件 4. 生成转介工单 5. 发送短信通知心理专员</v>
+        <v>停止常规建议输出,提示转入学生个体问题模块,通知年级组长,记录安全事件</v>
       </c>
       <c r="G2" t="str">
-        <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>
+        <v>完成全班关系筛查且年级组长确认无欺凌情形</v>
       </c>
       <c r="H2" t="str">
-        <v>心理专员</v>
+        <v>年级组长</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在班级系统建设评估中触发红线：纪律与凝聚力双低。请尽快登录系统查看工单。</v>
+        <v>[班级]关系系统评估触发红线，请安排逐个学生筛查。</v>
       </c>
       <c r="J2" t="str">
-        <v>PRD 8.3</v>
+        <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/class_system/attribution.xlsx
+++ b/business-libraries/test-data/class_system/attribution.xlsx
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1197,51 +1197,183 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_GRADE_MATURE</v>
+        <v>CS_GRADE_ENERGY_SURVIVAL</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D5" t="str">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>mature</v>
+        <v>survival</v>
       </c>
       <c r="G5" t="str">
-        <v>成熟期</v>
+        <v>生存期</v>
       </c>
       <c r="H5" t="str">
-        <v>low</v>
+        <v>crisis</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>班级系统运行成熟，建议把已有经验沉淀成可交接的班级手册。</v>
+        <v>能量场问卷显示班级秩序高度依赖教师在场，先稳住秩序再谈建设。</v>
       </c>
       <c r="K5" t="str">
-        <v>复评退回运行期以下</v>
+        <v>连续两次仍为生存期</v>
       </c>
       <c r="L5" t="str">
         <v>年级组长</v>
       </c>
       <c r="M5" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N5" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CS_GRADE_ENERGY_NORMING</v>
+      </c>
+      <c r="B6" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C6" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="D6" t="str">
+        <v>25</v>
+      </c>
+      <c r="E6" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F6" t="str">
+        <v>norming</v>
+      </c>
+      <c r="G6" t="str">
+        <v>规范期</v>
+      </c>
+      <c r="H6" t="str">
+        <v>high</v>
+      </c>
+      <c r="I6" t="str">
+        <v>否</v>
+      </c>
+      <c r="J6" t="str">
+        <v>班级能量场存在明显薄弱环节，重点是补成可重复执行的机制。</v>
+      </c>
+      <c r="K6" t="str">
+        <v>连续两次仍为规范期</v>
+      </c>
+      <c r="L6" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M6" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N6" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CS_GRADE_ENERGY_OPERATING</v>
+      </c>
+      <c r="B7" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CS_ENERGY</v>
+      </c>
+      <c r="D7" t="str">
+        <v>35</v>
+      </c>
+      <c r="E7" t="str">
+        <v>均分 &gt;= 2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>operating</v>
+      </c>
+      <c r="G7" t="str">
+        <v>运行期</v>
+      </c>
+      <c r="H7" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>班级能量场基本稳定，可聚焦单个环节做精细建设。</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_GRADE_MATURE</v>
+      </c>
+      <c r="B8" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>999</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>mature</v>
+      </c>
+      <c r="G8" t="str">
+        <v>成熟期</v>
+      </c>
+      <c r="H8" t="str">
+        <v>low</v>
+      </c>
+      <c r="I8" t="str">
+        <v>否</v>
+      </c>
+      <c r="J8" t="str">
+        <v>班级系统运行成熟，建议把已有经验沉淀成可交接的班级手册。</v>
+      </c>
+      <c r="K8" t="str">
+        <v>复评退回运行期以下</v>
+      </c>
+      <c r="L8" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M8" t="str">
         <v>90天后复评</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N8" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/class_system/attribution.xlsx
+++ b/business-libraries/test-data/class_system/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>均分</v>
       </c>
       <c r="D2" t="str">
-        <v>五系统整体均分，越高表示越薄弱</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>目标系统未落地</v>
@@ -526,10 +526,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>组织系统缺位</v>
+        <v>权力系统缺位</v>
       </c>
       <c r="C3" t="str">
         <v>class_system</v>
@@ -558,10 +558,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>活动系统空转</v>
+        <v>情感系统空转</v>
       </c>
       <c r="C4" t="str">
         <v>class_system</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="B5" t="str">
-        <v>环境系统薄弱</v>
+        <v>规范系统薄弱</v>
       </c>
       <c r="C5" t="str">
         <v>class_system</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>关系系统受损</v>
@@ -652,16 +652,48 @@
         <v>班级系统建设手册v1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>堰塞湖蓄积风险</v>
+      </c>
+      <c r="C7" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="str">
+        <v>class_system,warning,dam</v>
+      </c>
+      <c r="F7" t="str">
+        <v>情绪、冲突、需求、声音四类信号被截断，问题在水面下蓄积，存在突发爆发的风险。</v>
+      </c>
+      <c r="G7" t="str">
+        <v>班级表面平静但氛围压抑；小事突然引爆；部分学生长期沉默</v>
+      </c>
+      <c r="H7" t="str">
+        <v>缺少情绪出口、冲突解决路径、需求回应机制和公平的表达通道</v>
+      </c>
+      <c r="I7" t="str">
+        <v>本周内为被截断的信号打开一个具体出口（情绪疏导会/冲突修复/需求征集/声音通道），并在两周内复评</v>
+      </c>
+      <c r="J7" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -691,13 +723,13 @@
         <v>CS_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[CS_GOAL] &gt;= 4</v>
+        <v>维度[CS_S1D1] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>2.5</v>
@@ -714,13 +746,13 @@
         <v>CS_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[CS_GOAL] &gt;= 3</v>
+        <v>维度[CS_S1D1] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,19 +769,19 @@
         <v>CS_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[CS_ORG] &gt;= 4</v>
+        <v>维度[CS_S1D2] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>2.5</v>
       </c>
       <c r="F4" t="str">
-        <v>组织系统得分处于高位，事务过度集中在教师身上</v>
+        <v>权力系统得分处于高位，事务过度集中在教师身上</v>
       </c>
       <c r="G4" t="str">
         <v>班级系统建设手册v1</v>
@@ -760,19 +792,19 @@
         <v>CS_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[CS_ORG] &gt;= 3</v>
+        <v>维度[CS_S1D2] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>组织系统存在待建设的环节</v>
+        <v>权力系统存在待建设的环节</v>
       </c>
       <c r="G5" t="str">
         <v>班级系统建设手册v1</v>
@@ -783,19 +815,19 @@
         <v>CS_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[CS_ACTIVITY] &gt;= 4</v>
+        <v>维度[CS_S1D3] &gt;= 4</v>
       </c>
       <c r="E6" t="str">
         <v>2.5</v>
       </c>
       <c r="F6" t="str">
-        <v>活动系统得分处于高位，活动缺少回应与复盘</v>
+        <v>情感系统得分处于高位，活动缺少回应与复盘</v>
       </c>
       <c r="G6" t="str">
         <v>班级系统建设手册v1</v>
@@ -806,19 +838,19 @@
         <v>CS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[CS_ACTIVITY] &gt;= 3</v>
+        <v>维度[CS_S1D3] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>活动系统存在待建设的环节</v>
+        <v>情感系统存在待建设的环节</v>
       </c>
       <c r="G7" t="str">
         <v>班级系统建设手册v1</v>
@@ -829,19 +861,19 @@
         <v>CS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[CS_ENV] &gt;= 4</v>
+        <v>维度[CS_S1D4] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>2.5</v>
       </c>
       <c r="F8" t="str">
-        <v>环境系统得分处于高位，秩序难以自主恢复</v>
+        <v>规范系统得分处于高位，秩序难以自主恢复</v>
       </c>
       <c r="G8" t="str">
         <v>班级系统建设手册v1</v>
@@ -852,19 +884,19 @@
         <v>CS_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[CS_ENV] &gt;= 3</v>
+        <v>维度[CS_S1D4] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>环境系统存在待建设的环节</v>
+        <v>规范系统存在待建设的环节</v>
       </c>
       <c r="G9" t="str">
         <v>班级系统建设手册v1</v>
@@ -875,13 +907,13 @@
         <v>CS_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[CS_RELATION] &gt;= 4</v>
+        <v>维度[CS_S1D5] &gt;= 4</v>
       </c>
       <c r="E10" t="str">
         <v>3</v>
@@ -898,13 +930,13 @@
         <v>CS_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[CS_RELATION] &gt;= 3</v>
+        <v>维度[CS_S1D5] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -918,16 +950,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_EV_21</v>
+        <v>CS_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C12" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[CS_ORDER] &gt;= 3.5</v>
+        <v>维度[CS_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
         <v>2</v>
@@ -941,22 +973,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_EV_22</v>
+        <v>CS_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="C13" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[CS_ORDER] &gt;= 3</v>
+        <v>维度[CS_S2D1] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1.5</v>
       </c>
       <c r="F13" t="str">
-        <v>秩序对教师在场的依赖提示组织系统缺位</v>
+        <v>秩序对教师在场的依赖提示权力系统缺位</v>
       </c>
       <c r="G13" t="str">
         <v>班级系统建设手册v1</v>
@@ -964,16 +996,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_EV_23</v>
+        <v>CS_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C14" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[CS_CONNECT] &gt;= 3.5</v>
+        <v>维度[CS_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
@@ -987,16 +1019,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_EV_24</v>
+        <v>CS_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="C15" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[CS_LEARNING] &gt;= 3.5</v>
+        <v>维度[CS_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2</v>
@@ -1008,16 +1040,108 @@
         <v>班级系统建设手册v1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_EV_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C16" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D16" t="str">
+        <v>题[q1] &gt;= 4</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>情绪被反复压制，缺少表达出口</v>
+      </c>
+      <c r="G16" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_EV_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C17" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D17" t="str">
+        <v>题[q2] &gt;= 4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F17" t="str">
+        <v>冲突被掩盖或回避，缺少正式解决路径</v>
+      </c>
+      <c r="G17" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_EV_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C18" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D18" t="str">
+        <v>题[q3] &gt;= 4</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F18" t="str">
+        <v>需求提出后长期得不到回应</v>
+      </c>
+      <c r="G18" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_EV_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C19" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D19" t="str">
+        <v>题[q4] &gt;= 4</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F19" t="str">
+        <v>部分学生的声音完全听不到</v>
+      </c>
+      <c r="G19" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1065,43 +1189,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_GRADE_SURVIVAL</v>
+        <v>CS_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>系统均分 &gt;= 4</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>survival</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>生存期</v>
+        <v>危机干预</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>班级多个子系统同时薄弱，当前处于生存期，需要先稳住秩序再谈建设。</v>
+        <v>班级系统整体处于危机水平，需立即干预</v>
       </c>
       <c r="K2" t="str">
-        <v>连续两次生存期</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v>班级系统建设手册v1</v>
@@ -1109,25 +1233,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_GRADE_NORMING</v>
+        <v>CS_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>class_system</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>系统均分 &gt;= 3.2</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F3" t="str">
-        <v>norming</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>规范期</v>
+        <v>秩序奠基</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1136,16 +1260,16 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>班级处于规范期，重点是把薄弱系统补成可重复执行的机制。</v>
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次规范期</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M3" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N3" t="str">
         <v>班级系统建设手册v1</v>
@@ -1153,25 +1277,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_GRADE_OPERATING</v>
+        <v>CS_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>class_system</v>
       </c>
       <c r="C4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>系统均分 &gt;= 2.4</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F4" t="str">
-        <v>operating</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>运行期</v>
+        <v>关系激活</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1180,16 +1304,16 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>班级基本能够自主运行，可以聚焦单个子系统做精细建设。</v>
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
       </c>
       <c r="K4" t="str">
-        <v>复评退回规范期或生存期</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>60天后复评</v>
+        <v/>
       </c>
       <c r="N4" t="str">
         <v>班级系统建设手册v1</v>
@@ -1197,43 +1321,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_GRADE_ENERGY_SURVIVAL</v>
+        <v>CS_GR_04</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F5" t="str">
-        <v>survival</v>
+        <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>生存期</v>
+        <v>制度自转</v>
       </c>
       <c r="H5" t="str">
-        <v>crisis</v>
+        <v>low</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>能量场问卷显示班级秩序高度依赖教师在场，先稳住秩序再谈建设。</v>
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次仍为生存期</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v>班级系统建设手册v1</v>
@@ -1241,25 +1365,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_GRADE_ENERGY_NORMING</v>
+        <v>CS_GR_AUTO_01</v>
       </c>
       <c r="B6" t="str">
         <v>class_system</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F6" t="str">
-        <v>norming</v>
+        <v>orange</v>
       </c>
       <c r="G6" t="str">
-        <v>规范期</v>
+        <v>秩序奠基</v>
       </c>
       <c r="H6" t="str">
         <v>high</v>
@@ -1268,16 +1392,16 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>班级能量场存在明显薄弱环节，重点是补成可重复执行的机制。</v>
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
       </c>
       <c r="K6" t="str">
-        <v>连续两次仍为规范期</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v>班级系统建设手册v1</v>
@@ -1285,25 +1409,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_GRADE_ENERGY_OPERATING</v>
+        <v>CS_GR_AUTO_02</v>
       </c>
       <c r="B7" t="str">
         <v>class_system</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D7" t="str">
-        <v>35</v>
+        <v>502</v>
       </c>
       <c r="E7" t="str">
-        <v>均分 &gt;= 2</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F7" t="str">
-        <v>operating</v>
+        <v>yellow</v>
       </c>
       <c r="G7" t="str">
-        <v>运行期</v>
+        <v>关系激活</v>
       </c>
       <c r="H7" t="str">
         <v>medium</v>
@@ -1312,7 +1436,7 @@
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>班级能量场基本稳定，可聚焦单个环节做精细建设。</v>
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -1329,25 +1453,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_GRADE_MATURE</v>
+        <v>CS_GR_AUTO_03</v>
       </c>
       <c r="B8" t="str">
         <v>class_system</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>CS_S2</v>
       </c>
       <c r="D8" t="str">
-        <v>999</v>
+        <v>503</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F8" t="str">
-        <v>mature</v>
+        <v>blue</v>
       </c>
       <c r="G8" t="str">
-        <v>成熟期</v>
+        <v>制度自转</v>
       </c>
       <c r="H8" t="str">
         <v>low</v>
@@ -1356,24 +1480,332 @@
         <v>否</v>
       </c>
       <c r="J8" t="str">
-        <v>班级系统运行成熟，建议把已有经验沉淀成可交接的班级手册。</v>
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
       </c>
       <c r="K8" t="str">
-        <v>复评退回运行期以下</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>90天后复评</v>
+        <v/>
       </c>
       <c r="N8" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_GR_AUTO_04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D9" t="str">
+        <v>504</v>
+      </c>
+      <c r="E9" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F9" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G9" t="str">
+        <v>秩序奠基</v>
+      </c>
+      <c r="H9" t="str">
+        <v>high</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_GR_AUTO_05</v>
+      </c>
+      <c r="B10" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D10" t="str">
+        <v>505</v>
+      </c>
+      <c r="E10" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G10" t="str">
+        <v>关系激活</v>
+      </c>
+      <c r="H10" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I10" t="str">
+        <v>否</v>
+      </c>
+      <c r="J10" t="str">
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_GR_AUTO_06</v>
+      </c>
+      <c r="B11" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C11" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D11" t="str">
+        <v>506</v>
+      </c>
+      <c r="E11" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G11" t="str">
+        <v>制度自转</v>
+      </c>
+      <c r="H11" t="str">
+        <v>low</v>
+      </c>
+      <c r="I11" t="str">
+        <v>否</v>
+      </c>
+      <c r="J11" t="str">
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_GR_AUTO_07</v>
+      </c>
+      <c r="B12" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C12" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="D12" t="str">
+        <v>507</v>
+      </c>
+      <c r="E12" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G12" t="str">
+        <v>秩序奠基</v>
+      </c>
+      <c r="H12" t="str">
+        <v>high</v>
+      </c>
+      <c r="I12" t="str">
+        <v>否</v>
+      </c>
+      <c r="J12" t="str">
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_GR_AUTO_08</v>
+      </c>
+      <c r="B13" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="D13" t="str">
+        <v>508</v>
+      </c>
+      <c r="E13" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G13" t="str">
+        <v>关系激活</v>
+      </c>
+      <c r="H13" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I13" t="str">
+        <v>否</v>
+      </c>
+      <c r="J13" t="str">
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_GR_AUTO_09</v>
+      </c>
+      <c r="B14" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="D14" t="str">
+        <v>509</v>
+      </c>
+      <c r="E14" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F14" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G14" t="str">
+        <v>制度自转</v>
+      </c>
+      <c r="H14" t="str">
+        <v>low</v>
+      </c>
+      <c r="I14" t="str">
+        <v>否</v>
+      </c>
+      <c r="J14" t="str">
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_GR_DEFAULT</v>
+      </c>
+      <c r="B15" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>999</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>green</v>
+      </c>
+      <c r="G15" t="str">
+        <v>文化引领</v>
+      </c>
+      <c r="H15" t="str">
+        <v>low</v>
+      </c>
+      <c r="I15" t="str">
+        <v>否</v>
+      </c>
+      <c r="J15" t="str">
+        <v>本次评估未发现需要重点干预的信号</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1419,19 +1851,19 @@
         <v>class_system</v>
       </c>
       <c r="B2" t="str">
-        <v>维度[CS_RELATION] &gt;= 4.7</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="C2" t="str">
-        <v>关系系统极端薄弱，可能存在校园欺凌或严重孤立</v>
+        <v>班级系统整体处于危机水平，需立即干预</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>暂停常规班级建设建议，转入学生个体问题模块做逐个筛查，并通知年级组长</v>
+        <v>联系年级组长与心理专员，暂停非必要活动</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出,提示转入学生个体问题模块,通知年级组长,记录安全事件</v>
+        <v>停止常规建议输出；提示转入学生个体问题模块；通知年级组长；记录安全事件</v>
       </c>
       <c r="G2" t="str">
         <v>完成全班关系筛查且年级组长确认无欺凌情形</v>
@@ -1440,7 +1872,7 @@
         <v>年级组长</v>
       </c>
       <c r="I2" t="str">
-        <v>[班级]关系系统评估触发红线，请安排逐个学生筛查。</v>
+        <v>[教师姓名]老师在班级系统评估中触发红线，请尽快登录系统查看处置要求。</v>
       </c>
       <c r="J2" t="str">
         <v>班级系统建设手册v1</v>

--- a/business-libraries/test-data/class_system/attribution.xlsx
+++ b/business-libraries/test-data/class_system/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>均分</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>五系统整体均分，越高表示越薄弱</v>
       </c>
       <c r="E2" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_AT_01</v>
+        <v>CS_AT_GOAL</v>
       </c>
       <c r="B2" t="str">
         <v>目标系统未落地</v>
@@ -526,10 +526,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="B3" t="str">
-        <v>权力系统缺位</v>
+        <v>组织系统缺位</v>
       </c>
       <c r="C3" t="str">
         <v>class_system</v>
@@ -558,10 +558,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_AT_03</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="B4" t="str">
-        <v>情感系统空转</v>
+        <v>活动系统空转</v>
       </c>
       <c r="C4" t="str">
         <v>class_system</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="B5" t="str">
-        <v>规范系统薄弱</v>
+        <v>环境系统薄弱</v>
       </c>
       <c r="C5" t="str">
         <v>class_system</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_RELATION</v>
       </c>
       <c r="B6" t="str">
         <v>关系系统受损</v>
@@ -652,48 +652,16 @@
         <v>班级系统建设手册v1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>CS_AT_06</v>
-      </c>
-      <c r="B7" t="str">
-        <v>堰塞湖蓄积风险</v>
-      </c>
-      <c r="C7" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="E7" t="str">
-        <v>class_system,warning,dam</v>
-      </c>
-      <c r="F7" t="str">
-        <v>情绪、冲突、需求、声音四类信号被截断，问题在水面下蓄积，存在突发爆发的风险。</v>
-      </c>
-      <c r="G7" t="str">
-        <v>班级表面平静但氛围压抑；小事突然引爆；部分学生长期沉默</v>
-      </c>
-      <c r="H7" t="str">
-        <v>缺少情绪出口、冲突解决路径、需求回应机制和公平的表达通道</v>
-      </c>
-      <c r="I7" t="str">
-        <v>本周内为被截断的信号打开一个具体出口（情绪疏导会/冲突修复/需求征集/声音通道），并在两周内复评</v>
-      </c>
-      <c r="J7" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -723,13 +691,13 @@
         <v>CS_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>CS_AT_01</v>
+        <v>CS_AT_GOAL</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[CS_S1D1] &gt;= 4</v>
+        <v>维度[CS_GOAL] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>2.5</v>
@@ -746,13 +714,13 @@
         <v>CS_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>CS_AT_01</v>
+        <v>CS_AT_GOAL</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[CS_S1D1] &gt;= 3</v>
+        <v>维度[CS_GOAL] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -769,19 +737,19 @@
         <v>CS_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="C4" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[CS_S1D2] &gt;= 4</v>
+        <v>维度[CS_ORG] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>2.5</v>
       </c>
       <c r="F4" t="str">
-        <v>权力系统得分处于高位，事务过度集中在教师身上</v>
+        <v>组织系统得分处于高位，事务过度集中在教师身上</v>
       </c>
       <c r="G4" t="str">
         <v>班级系统建设手册v1</v>
@@ -792,19 +760,19 @@
         <v>CS_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[CS_S1D2] &gt;= 3</v>
+        <v>维度[CS_ORG] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>权力系统存在待建设的环节</v>
+        <v>组织系统存在待建设的环节</v>
       </c>
       <c r="G5" t="str">
         <v>班级系统建设手册v1</v>
@@ -815,19 +783,19 @@
         <v>CS_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>CS_AT_03</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[CS_S1D3] &gt;= 4</v>
+        <v>维度[CS_ACTIVITY] &gt;= 4</v>
       </c>
       <c r="E6" t="str">
         <v>2.5</v>
       </c>
       <c r="F6" t="str">
-        <v>情感系统得分处于高位，活动缺少回应与复盘</v>
+        <v>活动系统得分处于高位，活动缺少回应与复盘</v>
       </c>
       <c r="G6" t="str">
         <v>班级系统建设手册v1</v>
@@ -838,19 +806,19 @@
         <v>CS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>CS_AT_03</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[CS_S1D3] &gt;= 3</v>
+        <v>维度[CS_ACTIVITY] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>情感系统存在待建设的环节</v>
+        <v>活动系统存在待建设的环节</v>
       </c>
       <c r="G7" t="str">
         <v>班级系统建设手册v1</v>
@@ -861,19 +829,19 @@
         <v>CS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="C8" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[CS_S1D4] &gt;= 4</v>
+        <v>维度[CS_ENV] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>2.5</v>
       </c>
       <c r="F8" t="str">
-        <v>规范系统得分处于高位，秩序难以自主恢复</v>
+        <v>环境系统得分处于高位，秩序难以自主恢复</v>
       </c>
       <c r="G8" t="str">
         <v>班级系统建设手册v1</v>
@@ -884,19 +852,19 @@
         <v>CS_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="C9" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[CS_S1D4] &gt;= 3</v>
+        <v>维度[CS_ENV] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>规范系统存在待建设的环节</v>
+        <v>环境系统存在待建设的环节</v>
       </c>
       <c r="G9" t="str">
         <v>班级系统建设手册v1</v>
@@ -907,13 +875,13 @@
         <v>CS_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_RELATION</v>
       </c>
       <c r="C10" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[CS_S1D5] &gt;= 4</v>
+        <v>维度[CS_RELATION] &gt;= 4</v>
       </c>
       <c r="E10" t="str">
         <v>3</v>
@@ -930,13 +898,13 @@
         <v>CS_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_RELATION</v>
       </c>
       <c r="C11" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[CS_S1D5] &gt;= 3</v>
+        <v>维度[CS_RELATION] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -950,16 +918,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_EV_11</v>
+        <v>CS_EV_21</v>
       </c>
       <c r="B12" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_ENV</v>
       </c>
       <c r="C12" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[CS_S2D1] &gt;= 3.5</v>
+        <v>维度[CS_ORDER] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
         <v>2</v>
@@ -973,22 +941,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_EV_12</v>
+        <v>CS_EV_22</v>
       </c>
       <c r="B13" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_ORG</v>
       </c>
       <c r="C13" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[CS_S2D1] &gt;= 3</v>
+        <v>维度[CS_ORDER] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1.5</v>
       </c>
       <c r="F13" t="str">
-        <v>秩序对教师在场的依赖提示权力系统缺位</v>
+        <v>秩序对教师在场的依赖提示组织系统缺位</v>
       </c>
       <c r="G13" t="str">
         <v>班级系统建设手册v1</v>
@@ -996,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_EV_13</v>
+        <v>CS_EV_23</v>
       </c>
       <c r="B14" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_RELATION</v>
       </c>
       <c r="C14" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[CS_S2D3] &gt;= 3.5</v>
+        <v>维度[CS_CONNECT] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
@@ -1019,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_EV_14</v>
+        <v>CS_EV_24</v>
       </c>
       <c r="B15" t="str">
-        <v>CS_AT_03</v>
+        <v>CS_AT_ACTIVITY</v>
       </c>
       <c r="C15" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[CS_S2D2] &gt;= 3.5</v>
+        <v>维度[CS_LEARNING] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2</v>
@@ -1040,108 +1008,16 @@
         <v>班级系统建设手册v1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>CS_EV_15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>CS_AT_06</v>
-      </c>
-      <c r="C16" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D16" t="str">
-        <v>题[q1] &gt;= 4</v>
-      </c>
-      <c r="E16" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="F16" t="str">
-        <v>情绪被反复压制，缺少表达出口</v>
-      </c>
-      <c r="G16" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>CS_EV_16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>CS_AT_06</v>
-      </c>
-      <c r="C17" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D17" t="str">
-        <v>题[q2] &gt;= 4</v>
-      </c>
-      <c r="E17" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="F17" t="str">
-        <v>冲突被掩盖或回避，缺少正式解决路径</v>
-      </c>
-      <c r="G17" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>CS_EV_17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>CS_AT_06</v>
-      </c>
-      <c r="C18" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D18" t="str">
-        <v>题[q3] &gt;= 4</v>
-      </c>
-      <c r="E18" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="F18" t="str">
-        <v>需求提出后长期得不到回应</v>
-      </c>
-      <c r="G18" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>CS_EV_18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>CS_AT_06</v>
-      </c>
-      <c r="C19" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D19" t="str">
-        <v>题[q4] &gt;= 4</v>
-      </c>
-      <c r="E19" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="F19" t="str">
-        <v>部分学生的声音完全听不到</v>
-      </c>
-      <c r="G19" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1184,74 +1060,86 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_GR_01</v>
+        <v>CS_GRADE_SURVIVAL</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>系统均分 &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>survival</v>
       </c>
       <c r="G2" t="str">
-        <v>危机干预</v>
+        <v>生存期</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
       </c>
       <c r="I2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J2" t="str">
-        <v>班级系统整体处于危机水平，需立即干预</v>
+        <v>班级多个子系统同时薄弱，当前处于生存期，需要先稳住秩序再谈建设。</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>连续两次生存期</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>14天后复评</v>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_GR_02</v>
+        <v>CS_GRADE_NORMING</v>
       </c>
       <c r="B3" t="str">
         <v>class_system</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>系统均分 &gt;= 3.2</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>norming</v>
       </c>
       <c r="G3" t="str">
-        <v>秩序奠基</v>
+        <v>规范期</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1260,42 +1148,48 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+        <v>班级处于规范期，重点是把薄弱系统补成可重复执行的机制。</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>连续两次规范期</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>30天后复评</v>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_GR_03</v>
+        <v>CS_GRADE_OPERATING</v>
       </c>
       <c r="B4" t="str">
         <v>class_system</v>
       </c>
       <c r="C4" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>系统均分 &gt;= 2.4</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>operating</v>
       </c>
       <c r="G4" t="str">
-        <v>关系激活</v>
+        <v>运行期</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1304,86 +1198,98 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+        <v>班级基本能够自主运行，可以聚焦单个子系统做精细建设。</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>复评退回规范期或生存期</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>60天后复评</v>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_GR_04</v>
+        <v>CS_GRADE_ENERGY_SURVIVAL</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_S1</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D5" t="str">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>blue</v>
+        <v>survival</v>
       </c>
       <c r="G5" t="str">
-        <v>制度自转</v>
+        <v>生存期</v>
       </c>
       <c r="H5" t="str">
-        <v>low</v>
+        <v>crisis</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+        <v>能量场问卷显示班级秩序高度依赖教师在场，先稳住秩序再谈建设。</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>连续两次仍为生存期</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>14天后复评</v>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_GR_AUTO_01</v>
+        <v>CS_GRADE_ENERGY_NORMING</v>
       </c>
       <c r="B6" t="str">
         <v>class_system</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D6" t="str">
-        <v>501</v>
+        <v>25</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F6" t="str">
-        <v>orange</v>
+        <v>norming</v>
       </c>
       <c r="G6" t="str">
-        <v>秩序奠基</v>
+        <v>规范期</v>
       </c>
       <c r="H6" t="str">
         <v>high</v>
@@ -1392,42 +1298,48 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+        <v>班级能量场存在明显薄弱环节，重点是补成可重复执行的机制。</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>连续两次仍为规范期</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>30天后复评</v>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_GR_AUTO_02</v>
+        <v>CS_GRADE_ENERGY_OPERATING</v>
       </c>
       <c r="B7" t="str">
         <v>class_system</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="D7" t="str">
-        <v>502</v>
+        <v>35</v>
       </c>
       <c r="E7" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>均分 &gt;= 2</v>
       </c>
       <c r="F7" t="str">
-        <v>yellow</v>
+        <v>operating</v>
       </c>
       <c r="G7" t="str">
-        <v>关系激活</v>
+        <v>运行期</v>
       </c>
       <c r="H7" t="str">
         <v>medium</v>
@@ -1436,7 +1348,7 @@
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+        <v>班级能量场基本稳定，可聚焦单个环节做精细建设。</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -1448,30 +1360,36 @@
         <v/>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_GR_AUTO_03</v>
+        <v>CS_GRADE_MATURE</v>
       </c>
       <c r="B8" t="str">
         <v>class_system</v>
       </c>
       <c r="C8" t="str">
-        <v>CS_S2</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>503</v>
+        <v>999</v>
       </c>
       <c r="E8" t="str">
-        <v>均分 &gt;= 3</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>blue</v>
+        <v>mature</v>
       </c>
       <c r="G8" t="str">
-        <v>制度自转</v>
+        <v>成熟期</v>
       </c>
       <c r="H8" t="str">
         <v>low</v>
@@ -1480,332 +1398,30 @@
         <v>否</v>
       </c>
       <c r="J8" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+        <v>班级系统运行成熟，建议把已有经验沉淀成可交接的班级手册。</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>复评退回运行期以下</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>90天后复评</v>
       </c>
       <c r="N8" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CS_GR_AUTO_04</v>
-      </c>
-      <c r="B9" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C9" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D9" t="str">
-        <v>504</v>
-      </c>
-      <c r="E9" t="str">
-        <v>均分 &gt;= 4</v>
-      </c>
-      <c r="F9" t="str">
-        <v>orange</v>
-      </c>
-      <c r="G9" t="str">
-        <v>秩序奠基</v>
-      </c>
-      <c r="H9" t="str">
-        <v>high</v>
-      </c>
-      <c r="I9" t="str">
-        <v>否</v>
-      </c>
-      <c r="J9" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>CS_GR_AUTO_05</v>
-      </c>
-      <c r="B10" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C10" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D10" t="str">
-        <v>505</v>
-      </c>
-      <c r="E10" t="str">
-        <v>均分 &gt;= 3.5</v>
-      </c>
-      <c r="F10" t="str">
-        <v>yellow</v>
-      </c>
-      <c r="G10" t="str">
-        <v>关系激活</v>
-      </c>
-      <c r="H10" t="str">
-        <v>medium</v>
-      </c>
-      <c r="I10" t="str">
-        <v>否</v>
-      </c>
-      <c r="J10" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>CS_GR_AUTO_06</v>
-      </c>
-      <c r="B11" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C11" t="str">
-        <v>CS_S3</v>
-      </c>
-      <c r="D11" t="str">
-        <v>506</v>
-      </c>
-      <c r="E11" t="str">
-        <v>均分 &gt;= 3</v>
-      </c>
-      <c r="F11" t="str">
-        <v>blue</v>
-      </c>
-      <c r="G11" t="str">
-        <v>制度自转</v>
-      </c>
-      <c r="H11" t="str">
-        <v>low</v>
-      </c>
-      <c r="I11" t="str">
-        <v>否</v>
-      </c>
-      <c r="J11" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>CS_GR_AUTO_07</v>
-      </c>
-      <c r="B12" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C12" t="str">
-        <v>CS_S4</v>
-      </c>
-      <c r="D12" t="str">
-        <v>507</v>
-      </c>
-      <c r="E12" t="str">
-        <v>均分 &gt;= 4</v>
-      </c>
-      <c r="F12" t="str">
-        <v>orange</v>
-      </c>
-      <c r="G12" t="str">
-        <v>秩序奠基</v>
-      </c>
-      <c r="H12" t="str">
-        <v>high</v>
-      </c>
-      <c r="I12" t="str">
-        <v>否</v>
-      </c>
-      <c r="J12" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>CS_GR_AUTO_08</v>
-      </c>
-      <c r="B13" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C13" t="str">
-        <v>CS_S4</v>
-      </c>
-      <c r="D13" t="str">
-        <v>508</v>
-      </c>
-      <c r="E13" t="str">
-        <v>均分 &gt;= 3.5</v>
-      </c>
-      <c r="F13" t="str">
-        <v>yellow</v>
-      </c>
-      <c r="G13" t="str">
-        <v>关系激活</v>
-      </c>
-      <c r="H13" t="str">
-        <v>medium</v>
-      </c>
-      <c r="I13" t="str">
-        <v>否</v>
-      </c>
-      <c r="J13" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>CS_GR_AUTO_09</v>
-      </c>
-      <c r="B14" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C14" t="str">
-        <v>CS_S4</v>
-      </c>
-      <c r="D14" t="str">
-        <v>509</v>
-      </c>
-      <c r="E14" t="str">
-        <v>均分 &gt;= 3</v>
-      </c>
-      <c r="F14" t="str">
-        <v>blue</v>
-      </c>
-      <c r="G14" t="str">
-        <v>制度自转</v>
-      </c>
-      <c r="H14" t="str">
-        <v>low</v>
-      </c>
-      <c r="I14" t="str">
-        <v>否</v>
-      </c>
-      <c r="J14" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v>班级系统建设手册v1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>CS_GR_DEFAULT</v>
-      </c>
-      <c r="B15" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>999</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v>green</v>
-      </c>
-      <c r="G15" t="str">
-        <v>文化引领</v>
-      </c>
-      <c r="H15" t="str">
-        <v>low</v>
-      </c>
-      <c r="I15" t="str">
-        <v>否</v>
-      </c>
-      <c r="J15" t="str">
-        <v>本次评估未发现需要重点干预的信号</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1851,19 +1467,19 @@
         <v>class_system</v>
       </c>
       <c r="B2" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>维度[CS_RELATION] &gt;= 4.7</v>
       </c>
       <c r="C2" t="str">
-        <v>班级系统整体处于危机水平，需立即干预</v>
+        <v>关系系统极端薄弱，可能存在校园欺凌或严重孤立</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>联系年级组长与心理专员，暂停非必要活动</v>
+        <v>暂停常规班级建设建议，转入学生个体问题模块做逐个筛查，并通知年级组长</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出；提示转入学生个体问题模块；通知年级组长；记录安全事件</v>
+        <v>停止常规建议输出,提示转入学生个体问题模块,通知年级组长,记录安全事件</v>
       </c>
       <c r="G2" t="str">
         <v>完成全班关系筛查且年级组长确认无欺凌情形</v>
@@ -1872,7 +1488,7 @@
         <v>年级组长</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在班级系统评估中触发红线，请尽快登录系统查看处置要求。</v>
+        <v>[班级]关系系统评估触发红线，请安排逐个学生筛查。</v>
       </c>
       <c r="J2" t="str">
         <v>班级系统建设手册v1</v>

--- a/business-libraries/test-data/class_system/attribution.xlsx
+++ b/business-libraries/test-data/class_system/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>均分</v>
       </c>
       <c r="D2" t="str">
-        <v>五系统整体均分，越高表示越薄弱</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>目标系统未落地</v>
@@ -526,10 +526,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>组织系统缺位</v>
+        <v>权力系统缺位</v>
       </c>
       <c r="C3" t="str">
         <v>class_system</v>
@@ -558,10 +558,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>活动系统空转</v>
+        <v>情感系统空转</v>
       </c>
       <c r="C4" t="str">
         <v>class_system</v>
@@ -590,10 +590,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="B5" t="str">
-        <v>环境系统薄弱</v>
+        <v>规范系统薄弱</v>
       </c>
       <c r="C5" t="str">
         <v>class_system</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>关系系统受损</v>
@@ -652,16 +652,48 @@
         <v>班级系统建设手册v1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>堰塞湖蓄积风险</v>
+      </c>
+      <c r="C7" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="str">
+        <v>class_system,warning,dam</v>
+      </c>
+      <c r="F7" t="str">
+        <v>情绪、冲突、需求、声音四类信号被截断，问题在水面下蓄积，存在突发爆发的风险。</v>
+      </c>
+      <c r="G7" t="str">
+        <v>班级表面平静但氛围压抑；小事突然引爆；部分学生长期沉默</v>
+      </c>
+      <c r="H7" t="str">
+        <v>缺少情绪出口、冲突解决路径、需求回应机制和公平的表达通道</v>
+      </c>
+      <c r="I7" t="str">
+        <v>本周内为被截断的信号打开一个具体出口（情绪疏导会/冲突修复/需求征集/声音通道），并在两周内复评</v>
+      </c>
+      <c r="J7" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -691,13 +723,13 @@
         <v>CS_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[CS_GOAL] &gt;= 4</v>
+        <v>维度[CS_S1D1] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>2.5</v>
@@ -714,13 +746,13 @@
         <v>CS_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>CS_AT_GOAL</v>
+        <v>CS_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[CS_GOAL] &gt;= 3</v>
+        <v>维度[CS_S1D1] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,19 +769,19 @@
         <v>CS_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[CS_ORG] &gt;= 4</v>
+        <v>维度[CS_S1D2] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>2.5</v>
       </c>
       <c r="F4" t="str">
-        <v>组织系统得分处于高位，事务过度集中在教师身上</v>
+        <v>权力系统得分处于高位，事务过度集中在教师身上</v>
       </c>
       <c r="G4" t="str">
         <v>班级系统建设手册v1</v>
@@ -760,19 +792,19 @@
         <v>CS_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[CS_ORG] &gt;= 3</v>
+        <v>维度[CS_S1D2] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>组织系统存在待建设的环节</v>
+        <v>权力系统存在待建设的环节</v>
       </c>
       <c r="G5" t="str">
         <v>班级系统建设手册v1</v>
@@ -783,19 +815,19 @@
         <v>CS_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[CS_ACTIVITY] &gt;= 4</v>
+        <v>维度[CS_S1D3] &gt;= 4</v>
       </c>
       <c r="E6" t="str">
         <v>2.5</v>
       </c>
       <c r="F6" t="str">
-        <v>活动系统得分处于高位，活动缺少回应与复盘</v>
+        <v>情感系统得分处于高位，活动缺少回应与复盘</v>
       </c>
       <c r="G6" t="str">
         <v>班级系统建设手册v1</v>
@@ -806,19 +838,19 @@
         <v>CS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[CS_ACTIVITY] &gt;= 3</v>
+        <v>维度[CS_S1D3] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>活动系统存在待建设的环节</v>
+        <v>情感系统存在待建设的环节</v>
       </c>
       <c r="G7" t="str">
         <v>班级系统建设手册v1</v>
@@ -829,19 +861,19 @@
         <v>CS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[CS_ENV] &gt;= 4</v>
+        <v>维度[CS_S1D4] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>2.5</v>
       </c>
       <c r="F8" t="str">
-        <v>环境系统得分处于高位，秩序难以自主恢复</v>
+        <v>规范系统得分处于高位，秩序难以自主恢复</v>
       </c>
       <c r="G8" t="str">
         <v>班级系统建设手册v1</v>
@@ -852,19 +884,19 @@
         <v>CS_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[CS_ENV] &gt;= 3</v>
+        <v>维度[CS_S1D4] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>环境系统存在待建设的环节</v>
+        <v>规范系统存在待建设的环节</v>
       </c>
       <c r="G9" t="str">
         <v>班级系统建设手册v1</v>
@@ -875,13 +907,13 @@
         <v>CS_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[CS_RELATION] &gt;= 4</v>
+        <v>维度[CS_S1D5] &gt;= 4</v>
       </c>
       <c r="E10" t="str">
         <v>3</v>
@@ -898,13 +930,13 @@
         <v>CS_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[CS_RELATION] &gt;= 3</v>
+        <v>维度[CS_S1D5] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
         <v>1</v>
@@ -918,16 +950,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CS_EV_21</v>
+        <v>CS_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>CS_AT_ENV</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C12" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[CS_ORDER] &gt;= 3.5</v>
+        <v>维度[CS_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E12" t="str">
         <v>2</v>
@@ -941,22 +973,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CS_EV_22</v>
+        <v>CS_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>CS_AT_ORG</v>
+        <v>CS_AT_02</v>
       </c>
       <c r="C13" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[CS_ORDER] &gt;= 3</v>
+        <v>维度[CS_S2D1] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
         <v>1.5</v>
       </c>
       <c r="F13" t="str">
-        <v>秩序对教师在场的依赖提示组织系统缺位</v>
+        <v>秩序对教师在场的依赖提示权力系统缺位</v>
       </c>
       <c r="G13" t="str">
         <v>班级系统建设手册v1</v>
@@ -964,16 +996,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CS_EV_23</v>
+        <v>CS_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>CS_AT_RELATION</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C14" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[CS_CONNECT] &gt;= 3.5</v>
+        <v>维度[CS_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
@@ -987,16 +1019,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_EV_24</v>
+        <v>CS_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>CS_AT_ACTIVITY</v>
+        <v>CS_AT_03</v>
       </c>
       <c r="C15" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[CS_LEARNING] &gt;= 3.5</v>
+        <v>维度[CS_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2</v>
@@ -1008,16 +1040,108 @@
         <v>班级系统建设手册v1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_EV_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C16" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D16" t="str">
+        <v>题[q1] &gt;= 4</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>情绪被反复压制，缺少表达出口</v>
+      </c>
+      <c r="G16" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_EV_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C17" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D17" t="str">
+        <v>题[q2] &gt;= 4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F17" t="str">
+        <v>冲突被掩盖或回避，缺少正式解决路径</v>
+      </c>
+      <c r="G17" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_EV_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C18" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D18" t="str">
+        <v>题[q3] &gt;= 4</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F18" t="str">
+        <v>需求提出后长期得不到回应</v>
+      </c>
+      <c r="G18" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_EV_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CS_AT_06</v>
+      </c>
+      <c r="C19" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D19" t="str">
+        <v>题[q4] &gt;= 4</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F19" t="str">
+        <v>部分学生的声音完全听不到</v>
+      </c>
+      <c r="G19" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1071,43 +1195,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS_GRADE_SURVIVAL</v>
+        <v>CS_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>系统均分 &gt;= 4</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F2" t="str">
-        <v>survival</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>生存期</v>
+        <v>危机干预</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>班级多个子系统同时薄弱，当前处于生存期，需要先稳住秩序再谈建设。</v>
+        <v>班级系统整体处于危机水平，需立即干预</v>
       </c>
       <c r="K2" t="str">
-        <v>连续两次生存期</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -1121,25 +1245,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CS_GRADE_NORMING</v>
+        <v>CS_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>class_system</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>系统均分 &gt;= 3.2</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F3" t="str">
-        <v>norming</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>规范期</v>
+        <v>秩序奠基</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1148,16 +1272,16 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>班级处于规范期，重点是把薄弱系统补成可重复执行的机制。</v>
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次规范期</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M3" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -1171,25 +1295,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CS_GRADE_OPERATING</v>
+        <v>CS_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>class_system</v>
       </c>
       <c r="C4" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="D4" t="str">
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>系统均分 &gt;= 2.4</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F4" t="str">
-        <v>operating</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>运行期</v>
+        <v>关系激活</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1198,16 +1322,16 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>班级基本能够自主运行，可以聚焦单个子系统做精细建设。</v>
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
       </c>
       <c r="K4" t="str">
-        <v>复评退回规范期或生存期</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>60天后复评</v>
+        <v/>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -1221,43 +1345,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CS_GRADE_ENERGY_SURVIVAL</v>
+        <v>CS_GR_04</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F5" t="str">
-        <v>survival</v>
+        <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>生存期</v>
+        <v>制度自转</v>
       </c>
       <c r="H5" t="str">
-        <v>crisis</v>
+        <v>low</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>能量场问卷显示班级秩序高度依赖教师在场，先稳住秩序再谈建设。</v>
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次仍为生存期</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -1271,25 +1395,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CS_GRADE_ENERGY_NORMING</v>
+        <v>CS_GR_AUTO_01</v>
       </c>
       <c r="B6" t="str">
         <v>class_system</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F6" t="str">
-        <v>norming</v>
+        <v>orange</v>
       </c>
       <c r="G6" t="str">
-        <v>规范期</v>
+        <v>秩序奠基</v>
       </c>
       <c r="H6" t="str">
         <v>high</v>
@@ -1298,16 +1422,16 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>班级能量场存在明显薄弱环节，重点是补成可重复执行的机制。</v>
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
       </c>
       <c r="K6" t="str">
-        <v>连续两次仍为规范期</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -1321,25 +1445,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CS_GRADE_ENERGY_OPERATING</v>
+        <v>CS_GR_AUTO_02</v>
       </c>
       <c r="B7" t="str">
         <v>class_system</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="D7" t="str">
-        <v>35</v>
+        <v>502</v>
       </c>
       <c r="E7" t="str">
-        <v>均分 &gt;= 2</v>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F7" t="str">
-        <v>operating</v>
+        <v>yellow</v>
       </c>
       <c r="G7" t="str">
-        <v>运行期</v>
+        <v>关系激活</v>
       </c>
       <c r="H7" t="str">
         <v>medium</v>
@@ -1348,7 +1472,7 @@
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>班级能量场基本稳定，可聚焦单个环节做精细建设。</v>
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -1371,25 +1495,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CS_GRADE_MATURE</v>
+        <v>CS_GR_AUTO_03</v>
       </c>
       <c r="B8" t="str">
         <v>class_system</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>CS_S2</v>
       </c>
       <c r="D8" t="str">
-        <v>999</v>
+        <v>503</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F8" t="str">
-        <v>mature</v>
+        <v>blue</v>
       </c>
       <c r="G8" t="str">
-        <v>成熟期</v>
+        <v>制度自转</v>
       </c>
       <c r="H8" t="str">
         <v>low</v>
@@ -1398,16 +1522,16 @@
         <v>否</v>
       </c>
       <c r="J8" t="str">
-        <v>班级系统运行成熟，建议把已有经验沉淀成可交接的班级手册。</v>
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
       </c>
       <c r="K8" t="str">
-        <v>复评退回运行期以下</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>90天后复评</v>
+        <v/>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -1416,12 +1540,362 @@
         <v/>
       </c>
       <c r="P8" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_GR_AUTO_04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D9" t="str">
+        <v>504</v>
+      </c>
+      <c r="E9" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F9" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G9" t="str">
+        <v>秩序奠基</v>
+      </c>
+      <c r="H9" t="str">
+        <v>high</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_GR_AUTO_05</v>
+      </c>
+      <c r="B10" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D10" t="str">
+        <v>505</v>
+      </c>
+      <c r="E10" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G10" t="str">
+        <v>关系激活</v>
+      </c>
+      <c r="H10" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I10" t="str">
+        <v>否</v>
+      </c>
+      <c r="J10" t="str">
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_GR_AUTO_06</v>
+      </c>
+      <c r="B11" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C11" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D11" t="str">
+        <v>506</v>
+      </c>
+      <c r="E11" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F11" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G11" t="str">
+        <v>制度自转</v>
+      </c>
+      <c r="H11" t="str">
+        <v>low</v>
+      </c>
+      <c r="I11" t="str">
+        <v>否</v>
+      </c>
+      <c r="J11" t="str">
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_GR_AUTO_07</v>
+      </c>
+      <c r="B12" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C12" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="D12" t="str">
+        <v>507</v>
+      </c>
+      <c r="E12" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G12" t="str">
+        <v>秩序奠基</v>
+      </c>
+      <c r="H12" t="str">
+        <v>high</v>
+      </c>
+      <c r="I12" t="str">
+        <v>否</v>
+      </c>
+      <c r="J12" t="str">
+        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_GR_AUTO_08</v>
+      </c>
+      <c r="B13" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="D13" t="str">
+        <v>508</v>
+      </c>
+      <c r="E13" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G13" t="str">
+        <v>关系激活</v>
+      </c>
+      <c r="H13" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I13" t="str">
+        <v>否</v>
+      </c>
+      <c r="J13" t="str">
+        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_GR_AUTO_09</v>
+      </c>
+      <c r="B14" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CS_S4</v>
+      </c>
+      <c r="D14" t="str">
+        <v>509</v>
+      </c>
+      <c r="E14" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F14" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G14" t="str">
+        <v>制度自转</v>
+      </c>
+      <c r="H14" t="str">
+        <v>low</v>
+      </c>
+      <c r="I14" t="str">
+        <v>否</v>
+      </c>
+      <c r="J14" t="str">
+        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v>班级系统建设手册v1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_GR_DEFAULT</v>
+      </c>
+      <c r="B15" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>999</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>green</v>
+      </c>
+      <c r="G15" t="str">
+        <v>文化引领</v>
+      </c>
+      <c r="H15" t="str">
+        <v>low</v>
+      </c>
+      <c r="I15" t="str">
+        <v>否</v>
+      </c>
+      <c r="J15" t="str">
+        <v>本次评估未发现需要重点干预的信号</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
         <v>班级系统建设手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1467,19 +1941,19 @@
         <v>class_system</v>
       </c>
       <c r="B2" t="str">
-        <v>维度[CS_RELATION] &gt;= 4.7</v>
+        <v>量表[CS_S1].均分 &gt;= 4</v>
       </c>
       <c r="C2" t="str">
-        <v>关系系统极端薄弱，可能存在校园欺凌或严重孤立</v>
+        <v>班级系统整体处于危机水平，需立即干预</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>暂停常规班级建设建议，转入学生个体问题模块做逐个筛查，并通知年级组长</v>
+        <v>联系年级组长与心理专员，暂停非必要活动</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出,提示转入学生个体问题模块,通知年级组长,记录安全事件</v>
+        <v>停止常规建议输出；提示转入学生个体问题模块；通知年级组长；记录安全事件</v>
       </c>
       <c r="G2" t="str">
         <v>完成全班关系筛查且年级组长确认无欺凌情形</v>
@@ -1488,7 +1962,7 @@
         <v>年级组长</v>
       </c>
       <c r="I2" t="str">
-        <v>[班级]关系系统评估触发红线，请安排逐个学生筛查。</v>
+        <v>[教师姓名]老师在班级系统评估中触发红线，请尽快登录系统查看处置要求。</v>
       </c>
       <c r="J2" t="str">
         <v>班级系统建设手册v1</v>

--- a/business-libraries/test-data/class_system/attribution.xlsx
+++ b/business-libraries/test-data/class_system/attribution.xlsx
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -497,31 +497,31 @@
         <v>CS_AT_01</v>
       </c>
       <c r="B2" t="str">
-        <v>目标系统未落地</v>
+        <v>亲师依恋断裂</v>
       </c>
       <c r="C2" t="str">
         <v>class_system</v>
       </c>
       <c r="D2" t="str">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E2" t="str">
-        <v>class_system,goal</v>
+        <v>class_system,relationship,attachment</v>
       </c>
       <c r="F2" t="str">
-        <v>班级目标没有被学生理解，或没有转化为可观察的阶段性成果。</v>
+        <v>学生与班主任未形成安全依恋基地，遇困不求助、对抗权威，关系得分持续偏低。</v>
       </c>
       <c r="G2" t="str">
-        <v>学生说不出班级目标；目标只贴在墙上</v>
+        <v>连续2周零主动求助；遇困回避求助、对抗权威、不愿敞开心扉</v>
       </c>
       <c r="H2" t="str">
-        <v>目标由教师单方面制定且缺少里程碑拆解</v>
+        <v>亲师依恋未建立安全基地（家庭依恋不安全且师生关系未补偿）</v>
       </c>
       <c r="I2" t="str">
-        <v>把本学期目标拆成三个可观察的里程碑，与学生共同确认第一个</v>
+        <v>每日1次非评价性打招呼；设固定谈心时间(10min/周)；用「先跟后带」接住情绪再谈事</v>
       </c>
       <c r="J2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -529,31 +529,31 @@
         <v>CS_AT_02</v>
       </c>
       <c r="B3" t="str">
-        <v>权力系统缺位</v>
+        <v>同伴联结薄弱</v>
       </c>
       <c r="C3" t="str">
         <v>class_system</v>
       </c>
       <c r="D3" t="str">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="str">
-        <v>class_system,org</v>
+        <v>class_system,relationship,peer</v>
       </c>
       <c r="F3" t="str">
-        <v>班级事务过度集中在教师身上，学生岗位职责不清或无法稳定运转。</v>
+        <v>同伴支持网络缺失，冲突无缓冲层，易升级为排斥或孤立。</v>
       </c>
       <c r="G3" t="str">
-        <v>所有事都要教师亲自过问；班干部形同虚设</v>
+        <v>周冲突≥3次且调解失败率&gt;50%；小团体排斥、冲突升级无缓冲、孤立个体</v>
       </c>
       <c r="H3" t="str">
-        <v>岗位设置缺少职责说明和交接流程</v>
+        <v>同伴支持网络缺失、缺少冲突缓冲与调解机制</v>
       </c>
       <c r="I3" t="str">
-        <v>选一个日常事务，写清责任人、执行步骤、异常处理和复盘时间，试行一周</v>
+        <v>重排小组(异质搭配)；设「联结员」角色；每日合作任务打卡</v>
       </c>
       <c r="J3" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -561,31 +561,31 @@
         <v>CS_AT_03</v>
       </c>
       <c r="B4" t="str">
-        <v>情感系统空转</v>
+        <v>家校连接松散</v>
       </c>
       <c r="C4" t="str">
         <v>class_system</v>
       </c>
       <c r="D4" t="str">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="str">
-        <v>class_system,activity</v>
+        <v>class_system,relationship,family</v>
       </c>
       <c r="F4" t="str">
-        <v>班级活动没有回应学生真实需要，或缺少复盘导致无法沉淀。</v>
+        <v>家长参与度低、沟通单向，重要通知无闭环。</v>
       </c>
       <c r="G4" t="str">
-        <v>活动办完就结束，学生参与度低</v>
+        <v>关键通知24h响应率&lt;60%；家长失联、群内零响应、沟通单向</v>
       </c>
       <c r="H4" t="str">
-        <v>活动主题由教师指定且无复盘环节</v>
+        <v>家校双向连接松散、沟通单向无回执闭环</v>
       </c>
       <c r="I4" t="str">
-        <v>在下一次活动后加一个十分钟复盘，让学生说出一个保留动作和一个调整动作</v>
+        <v>用73855法则沟通；每周1条正向反馈；重要事项回执闭环</v>
       </c>
       <c r="J4" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +593,31 @@
         <v>CS_AT_04</v>
       </c>
       <c r="B5" t="str">
-        <v>规范系统薄弱</v>
+        <v>组织架构空缺</v>
       </c>
       <c r="C5" t="str">
         <v>class_system</v>
       </c>
       <c r="D5" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="str">
-        <v>class_system,environment</v>
+        <v>class_system,organization,structure</v>
       </c>
       <c r="F5" t="str">
-        <v>班级规则和空间布置无法支撑稳定的学习秩序。</v>
+        <v>班委/小组未建立或形同虚设，事事班主任兜底。</v>
       </c>
       <c r="G5" t="str">
-        <v>规则只贴在墙上；混乱后难以恢复</v>
+        <v>核心岗位空缺&gt;1周；班干部缺位、履职差、唯名不干事</v>
       </c>
       <c r="H5" t="str">
-        <v>规则由教师单方制定，缺少共同理解</v>
+        <v>选举即任命、无试用考核、岗位无职责说明</v>
       </c>
       <c r="I5" t="str">
-        <v>挑一条最常被违反的规则，和学生一起重新表述成可观察的行为标准</v>
+        <v>发布岗位说明书；自荐+竞选；1个月试用期+考核表；正式任命</v>
       </c>
       <c r="J5" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -625,31 +625,31 @@
         <v>CS_AT_05</v>
       </c>
       <c r="B6" t="str">
-        <v>关系系统受损</v>
+        <v>架构适配失当</v>
       </c>
       <c r="C6" t="str">
         <v>class_system</v>
       </c>
       <c r="D6" t="str">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E6" t="str">
-        <v>class_system,relation</v>
+        <v>class_system,organization,seating</v>
       </c>
       <c r="F6" t="str">
-        <v>学生之间的冲突难以修复，缺少稳定的同伴支持结构。</v>
+        <v>座位/分组未按特质与关系调整，引发冲突或搭便车。</v>
       </c>
       <c r="G6" t="str">
-        <v>冲突反复发生；存在被孤立的学生</v>
+        <v>组内贡献方差过大；排座冲突、小组失效、搭便车</v>
       </c>
       <c r="H6" t="str">
-        <v>缺少冲突处理流程和同伴互助机制</v>
+        <v>未按特质分组、排座无透明依据</v>
       </c>
       <c r="I6" t="str">
-        <v>建立一个固定的冲突修复流程，并在下一次冲突时完整走一遍</v>
+        <v>按特质与关系重排座位/小组；设互补搭档；周复盘适配度</v>
       </c>
       <c r="J6" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="7">
@@ -657,43 +657,331 @@
         <v>CS_AT_06</v>
       </c>
       <c r="B7" t="str">
-        <v>堰塞湖蓄积风险</v>
+        <v>运转机制失效</v>
       </c>
       <c r="C7" t="str">
         <v>class_system</v>
       </c>
       <c r="D7" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>class_system,organization,operation</v>
+      </c>
+      <c r="F7" t="str">
+        <v>值日/事务无标准流程，响应慢、易积压。</v>
+      </c>
+      <c r="G7" t="str">
+        <v>常规事务响应&gt;48h；值日推诿、事务积压、无人兜底</v>
+      </c>
+      <c r="H7" t="str">
+        <v>无运转SOP、岗位无责任人</v>
+      </c>
+      <c r="I7" t="str">
+        <v>列值日/事务清单与标准；设轮值负责人；日清日毕打卡</v>
+      </c>
+      <c r="J7" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_AT_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>公约悬空</v>
+      </c>
+      <c r="C8" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D8" t="str">
         <v>1.5</v>
       </c>
-      <c r="E7" t="str">
-        <v>class_system,warning,dam</v>
-      </c>
-      <c r="F7" t="str">
-        <v>情绪、冲突、需求、声音四类信号被截断，问题在水面下蓄积，存在突发爆发的风险。</v>
-      </c>
-      <c r="G7" t="str">
-        <v>班级表面平静但氛围压抑；小事突然引爆；部分学生长期沉默</v>
-      </c>
-      <c r="H7" t="str">
-        <v>缺少情绪出口、冲突解决路径、需求回应机制和公平的表达通道</v>
-      </c>
-      <c r="I7" t="str">
-        <v>本周内为被截断的信号打开一个具体出口（情绪疏导会/冲突修复/需求征集/声音通道），并在两周内复评</v>
-      </c>
-      <c r="J7" t="str">
-        <v>班级系统建设手册v1</v>
+      <c r="E8" t="str">
+        <v>class_system,norm,rules</v>
+      </c>
+      <c r="F8" t="str">
+        <v>公约未共建或建而不用，学生不知晓、无约束力。</v>
+      </c>
+      <c r="G8" t="str">
+        <v>知晓率&lt;70%或复发率&gt;40%；公约悬空、学生不知晓</v>
+      </c>
+      <c r="H8" t="str">
+        <v>未共建即张贴、公约上墙后缺乏复盘</v>
+      </c>
+      <c r="I8" t="str">
+        <v>公约六步法：草案征集→小组讨论→全班表决→上墙签名→月度复盘</v>
+      </c>
+      <c r="J8" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_AT_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>督导标准不一</v>
+      </c>
+      <c r="C9" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="E9" t="str">
+        <v>class_system,norm,supervision</v>
+      </c>
+      <c r="F9" t="str">
+        <v>同一行为不同老师/不同次处理不一致，学生无所适从、规则感崩塌。</v>
+      </c>
+      <c r="G9" t="str">
+        <v>同行为处置差异&gt;2级；同一行为不同处理、违规反复</v>
+      </c>
+      <c r="H9" t="str">
+        <v>督导标准不一、无统一行为清单与处置标准</v>
+      </c>
+      <c r="I9" t="str">
+        <v>公布行为清单与处置标准；师生共议边界；一致执行</v>
+      </c>
+      <c r="J9" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_AT_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>危机响应迟滞</v>
+      </c>
+      <c r="C10" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D10" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E10" t="str">
+        <v>class_system,norm,crisis</v>
+      </c>
+      <c r="F10" t="str">
+        <v>风险未识别或识别后升级缓慢，错过干预窗口。</v>
+      </c>
+      <c r="G10" t="str">
+        <v>达到C级仍未在24h内启动；风险迟报漏报、处置失当升级</v>
+      </c>
+      <c r="H10" t="str">
+        <v>危机识别清单未用、A-E响应流程缺失</v>
+      </c>
+      <c r="I10" t="str">
+        <v>按A-E填识别卡；B/C级48h内启动；记录与跟踪</v>
+      </c>
+      <c r="J10" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_AT_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>目标缺位</v>
+      </c>
+      <c r="C11" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E11" t="str">
+        <v>class_system,goal,target</v>
+      </c>
+      <c r="F11" t="str">
+        <v>班级/个人无清晰目标，努力无方向。</v>
+      </c>
+      <c r="G11" t="str">
+        <v>学期目标覆盖率&lt;80%；班级/个人无清晰目标、目标空泛</v>
+      </c>
+      <c r="H11" t="str">
+        <v>无目标金字塔、目标未拆解为里程碑</v>
+      </c>
+      <c r="I11" t="str">
+        <v>班→组→人三级拆解；SMART改写；周看板追踪</v>
+      </c>
+      <c r="J11" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_AT_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>动力错配</v>
+      </c>
+      <c r="C12" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E12" t="str">
+        <v>class_system,goal,motivation</v>
+      </c>
+      <c r="F12" t="str">
+        <v>能力-意愿组合误判，任务分配错位导致推诿或闲置。</v>
+      </c>
+      <c r="G12" t="str">
+        <v>高能力低意愿岗位闲置；任务分配与能力意愿错配、推一下动一下</v>
+      </c>
+      <c r="H12" t="str">
+        <v>未做动力矩阵、任务委派未按能力×意愿匹配</v>
+      </c>
+      <c r="I12" t="str">
+        <v>给每生画能力×意愿坐标；高能力低意愿→赋挑战岗；双低→降槛+陪跑</v>
+      </c>
+      <c r="J12" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_AT_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>学业堰塞</v>
+      </c>
+      <c r="C13" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D13" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E13" t="str">
+        <v>class_system,goal,learning</v>
+      </c>
+      <c r="F13" t="str">
+        <v>知识欠账累积成坝，后续学习链断裂。</v>
+      </c>
+      <c r="G13" t="str">
+        <v>模块得分率&lt;80%且连续失分；知识欠账堆积成坝、学习链断裂</v>
+      </c>
+      <c r="H13" t="str">
+        <v>欠账未溯源回填、缺堰塞湖疏浚机制</v>
+      </c>
+      <c r="I13" t="str">
+        <v>定位断点模块；降难度回填；每日1节点+错题重做</v>
+      </c>
+      <c r="J13" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_AT_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>氛围负向</v>
+      </c>
+      <c r="C14" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E14" t="str">
+        <v>class_system,emotion,climate</v>
+      </c>
+      <c r="F14" t="str">
+        <v>班级情绪基调消极，集体无温度、无正向仪式。</v>
+      </c>
+      <c r="G14" t="str">
+        <v>月度氛围评分&lt;3.5；冷漠、负向情绪弥漫、集体无温度</v>
+      </c>
+      <c r="H14" t="str">
+        <v>正向仪式感缺失、缺乏每日正向反馈机制</v>
+      </c>
+      <c r="I14" t="str">
+        <v>每日1句正向反馈；周班会亮点仪式；正念/颂钵3min</v>
+      </c>
+      <c r="J14" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_AT_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>个体情绪失接</v>
+      </c>
+      <c r="C15" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D15" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="E15" t="str">
+        <v>class_system,emotion,support</v>
+      </c>
+      <c r="F15" t="str">
+        <v>个体情绪问题未被及时接住，积压后爆发。</v>
+      </c>
+      <c r="G15" t="str">
+        <v>周转介&gt;2人且情绪角零使用；个体情绪问题无人接住、积压爆发</v>
+      </c>
+      <c r="H15" t="str">
+        <v>情绪角缺位、缺乏EQ型情绪承接机制</v>
+      </c>
+      <c r="I15" t="str">
+        <v>设情绪角；EQ型四步接住；每周情绪签到</v>
+      </c>
+      <c r="J15" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_AT_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>归属感缺失</v>
+      </c>
+      <c r="C16" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E16" t="str">
+        <v>class_system,emotion,belonging</v>
+      </c>
+      <c r="F16" t="str">
+        <v>边缘学生无连接通道，持续低参与、隐形。</v>
+      </c>
+      <c r="G16" t="str">
+        <v>持续2周零主动发言；边缘学生、低参与、隐形人</v>
+      </c>
+      <c r="H16" t="str">
+        <v>无连接通道、缺乏归属感建设机制</v>
+      </c>
+      <c r="I16" t="str">
+        <v>设固定搭档/导师；每日1次正向点名；安全岛角落</v>
+      </c>
+      <c r="J16" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -729,16 +1017,16 @@
         <v>CS_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[CS_S1D1] &gt;= 4</v>
+        <v>维度[CS_S1D1] &lt;= 3</v>
       </c>
       <c r="E2" t="str">
         <v>2.5</v>
       </c>
       <c r="F2" t="str">
-        <v>目标系统得分处于高位，目标未被学生理解或未落地</v>
+        <v>关系系统得分处于低位，师生信任与依恋基础薄弱</v>
       </c>
       <c r="G2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -749,19 +1037,19 @@
         <v>CS_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>CS_S1</v>
+        <v>CS_S8</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[CS_S1D1] &gt;= 3</v>
+        <v>题[q7] &gt;= 2 或 题[q9] &gt;= 2</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>目标系统存在待建设的环节</v>
+        <v>依恋观察显示回避型或混乱型特征，须警惕创伤背景</v>
       </c>
       <c r="G3" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -775,16 +1063,16 @@
         <v>CS_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[CS_S1D2] &gt;= 4</v>
+        <v>维度[CS_S1D1] &lt;= 3</v>
       </c>
       <c r="E4" t="str">
         <v>2.5</v>
       </c>
       <c r="F4" t="str">
-        <v>权力系统得分处于高位，事务过度集中在教师身上</v>
+        <v>关系系统低位，同伴互助与氛围不足</v>
       </c>
       <c r="G4" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -795,19 +1083,19 @@
         <v>CS_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_S1</v>
+        <v>CS_S2</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[CS_S1D2] &gt;= 3</v>
+        <v>维度[CS_S2D4] &lt;= 3</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>权力系统存在待建设的环节</v>
+        <v>能量场关系维度偏低，学生之间缺少正向联结</v>
       </c>
       <c r="G5" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -821,16 +1109,16 @@
         <v>CS_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[CS_S1D3] &gt;= 4</v>
+        <v>维度[CS_S1D1] &lt;= 3.5</v>
       </c>
       <c r="E6" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="str">
-        <v>情感系统得分处于高位，活动缺少回应与复盘</v>
+        <v>本模块无家校维度直接量表，以关系系统低位作为代理信号（家校连接松散需结合沟通记录确认）</v>
       </c>
       <c r="G6" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="7">
@@ -838,22 +1126,22 @@
         <v>CS_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>CS_AT_03</v>
+        <v>CS_AT_04</v>
       </c>
       <c r="C7" t="str">
         <v>CS_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[CS_S1D3] &gt;= 3</v>
+        <v>维度[CS_S1D2] &lt;= 3</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F7" t="str">
-        <v>情感系统存在待建设的环节</v>
+        <v>组织系统低位，班委与服务岗位运转不足</v>
       </c>
       <c r="G7" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="8">
@@ -861,22 +1149,22 @@
         <v>CS_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C8" t="str">
         <v>CS_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[CS_S1D4] &gt;= 4</v>
+        <v>维度[CS_S1D2] &lt;= 3.5</v>
       </c>
       <c r="E8" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F8" t="str">
-        <v>规范系统得分处于高位，秩序难以自主恢复</v>
+        <v>组织系统待建设，座位/分组适配存在风险</v>
       </c>
       <c r="G8" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="9">
@@ -884,22 +1172,22 @@
         <v>CS_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_05</v>
       </c>
       <c r="C9" t="str">
-        <v>CS_S1</v>
+        <v>CS_S2</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[CS_S1D4] &gt;= 3</v>
+        <v>维度[CS_S2D3] &lt;= 3</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="str">
-        <v>规范系统存在待建设的环节</v>
+        <v>行为维度偏低，参与度不足提示分组适配失当</v>
       </c>
       <c r="G9" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="10">
@@ -907,22 +1195,22 @@
         <v>CS_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_06</v>
       </c>
       <c r="C10" t="str">
         <v>CS_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[CS_S1D5] &gt;= 4</v>
+        <v>维度[CS_S1D2] &lt;= 3.5</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>关系系统得分处于高位，冲突难以修复</v>
+        <v>组织系统待建设，日常事务运转缺乏标准流程</v>
       </c>
       <c r="G10" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="11">
@@ -930,22 +1218,22 @@
         <v>CS_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_06</v>
       </c>
       <c r="C11" t="str">
-        <v>CS_S1</v>
+        <v>CS_S2</v>
       </c>
       <c r="D11" t="str">
-        <v>维度[CS_S1D5] &gt;= 3</v>
+        <v>维度[CS_S2D3] &lt;= 2.5</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F11" t="str">
-        <v>关系系统存在待建设的环节</v>
+        <v>行为维度明显偏低，指令响应与秩序依赖教师</v>
       </c>
       <c r="G11" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="12">
@@ -953,22 +1241,22 @@
         <v>CS_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>CS_AT_04</v>
+        <v>CS_AT_07</v>
       </c>
       <c r="C12" t="str">
-        <v>CS_S2</v>
+        <v>CS_S1</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[CS_S2D1] &gt;= 3.5</v>
+        <v>维度[CS_S1D3] &lt;= 3</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F12" t="str">
-        <v>能量场问卷显示秩序需要教师持续在场维持</v>
+        <v>规范系统低位，规则认同与执行不足</v>
       </c>
       <c r="G12" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="13">
@@ -976,22 +1264,22 @@
         <v>CS_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>CS_AT_02</v>
+        <v>CS_AT_08</v>
       </c>
       <c r="C13" t="str">
-        <v>CS_S2</v>
+        <v>CS_S1</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[CS_S2D1] &gt;= 3</v>
+        <v>维度[CS_S1D3] &lt;= 3.5</v>
       </c>
       <c r="E13" t="str">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>秩序对教师在场的依赖提示权力系统缺位</v>
+        <v>规范系统待建设，规则执行一致性存疑</v>
       </c>
       <c r="G13" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="14">
@@ -999,22 +1287,22 @@
         <v>CS_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>CS_AT_05</v>
+        <v>CS_AT_09</v>
       </c>
       <c r="C14" t="str">
-        <v>CS_S2</v>
+        <v>CS_S6</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[CS_S2D3] &gt;= 3.5</v>
+        <v>题[q3] == 1 或 题[q4] == 1</v>
       </c>
       <c r="E14" t="str">
         <v>2.5</v>
       </c>
       <c r="F14" t="str">
-        <v>能量场问卷显示学生之间缺少正向联结</v>
+        <v>点检命中 C 级或 D 级，存在风险识别与响应缺口</v>
       </c>
       <c r="G14" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="15">
@@ -1022,22 +1310,22 @@
         <v>CS_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>CS_AT_03</v>
+        <v>CS_AT_09</v>
       </c>
       <c r="C15" t="str">
-        <v>CS_S2</v>
+        <v>CS_S1</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[CS_S2D2] &gt;= 3.5</v>
+        <v>维度[CS_S1D3] &lt;= 3</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F15" t="str">
-        <v>学习投入依赖外部推动，活动未能激发内驱</v>
+        <v>规范系统低位，危机识别与响应机制薄弱</v>
       </c>
       <c r="G15" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="16">
@@ -1045,22 +1333,22 @@
         <v>CS_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>CS_AT_06</v>
+        <v>CS_AT_10</v>
       </c>
       <c r="C16" t="str">
-        <v>CS_S3</v>
+        <v>CS_S1</v>
       </c>
       <c r="D16" t="str">
-        <v>题[q1] &gt;= 4</v>
+        <v>维度[CS_S1D4] &lt;= 3</v>
       </c>
       <c r="E16" t="str">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F16" t="str">
-        <v>情绪被反复压制，缺少表达出口</v>
+        <v>目标系统低位，班级/个人目标不清晰</v>
       </c>
       <c r="G16" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="17">
@@ -1068,22 +1356,22 @@
         <v>CS_EV_16</v>
       </c>
       <c r="B17" t="str">
-        <v>CS_AT_06</v>
+        <v>CS_AT_11</v>
       </c>
       <c r="C17" t="str">
-        <v>CS_S3</v>
+        <v>CS_S1</v>
       </c>
       <c r="D17" t="str">
-        <v>题[q2] &gt;= 4</v>
+        <v>维度[CS_S1D4] &lt;= 3.5</v>
       </c>
       <c r="E17" t="str">
         <v>1.5</v>
       </c>
       <c r="F17" t="str">
-        <v>冲突被掩盖或回避，缺少正式解决路径</v>
+        <v>目标系统待建设，动力与目标衔接不足</v>
       </c>
       <c r="G17" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="18">
@@ -1091,22 +1379,22 @@
         <v>CS_EV_17</v>
       </c>
       <c r="B18" t="str">
-        <v>CS_AT_06</v>
+        <v>CS_AT_11</v>
       </c>
       <c r="C18" t="str">
-        <v>CS_S3</v>
+        <v>CS_S9</v>
       </c>
       <c r="D18" t="str">
-        <v>题[q3] &gt;= 4</v>
+        <v>题[q2] == 1 或 题[q3] == 1</v>
       </c>
       <c r="E18" t="str">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F18" t="str">
-        <v>需求提出后长期得不到回应</v>
+        <v>个案诊断为挫折型或对抗型，能力-意愿组合错配</v>
       </c>
       <c r="G18" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="19">
@@ -1114,34 +1402,195 @@
         <v>CS_EV_18</v>
       </c>
       <c r="B19" t="str">
-        <v>CS_AT_06</v>
+        <v>CS_AT_12</v>
       </c>
       <c r="C19" t="str">
-        <v>CS_S3</v>
+        <v>CS_S1</v>
       </c>
       <c r="D19" t="str">
-        <v>题[q4] &gt;= 4</v>
+        <v>维度[CS_S1D4] &lt;= 3.5</v>
       </c>
       <c r="E19" t="str">
         <v>1.5</v>
       </c>
       <c r="F19" t="str">
-        <v>部分学生的声音完全听不到</v>
+        <v>目标系统待建设，学习动力与目标不足（学业欠账需结合成绩数据确认）</v>
       </c>
       <c r="G19" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_EV_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>CS_AT_12</v>
+      </c>
+      <c r="C20" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="D20" t="str">
+        <v>维度[CS_S2D2] &lt;= 3</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2</v>
+      </c>
+      <c r="F20" t="str">
+        <v>认知维度偏低，学习投入与订正不足，存在欠账累积风险</v>
+      </c>
+      <c r="G20" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_EV_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>CS_AT_13</v>
+      </c>
+      <c r="C21" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="D21" t="str">
+        <v>维度[CS_S1D5] &lt;= 3</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F21" t="str">
+        <v>情感系统低位，归属感与集体温度不足</v>
+      </c>
+      <c r="G21" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_EV_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>CS_AT_13</v>
+      </c>
+      <c r="C22" t="str">
+        <v>CS_S2</v>
+      </c>
+      <c r="D22" t="str">
+        <v>维度[CS_S2D1] &lt;= 3</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2</v>
+      </c>
+      <c r="F22" t="str">
+        <v>能量场情感维度偏低，课堂氛围压抑</v>
+      </c>
+      <c r="G22" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_EV_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>CS_AT_14</v>
+      </c>
+      <c r="C23" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="D23" t="str">
+        <v>维度[CS_S1D5] &lt;= 3.5</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>情感系统待建设，个体情绪支持通道不足</v>
+      </c>
+      <c r="G23" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_EV_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>CS_AT_14</v>
+      </c>
+      <c r="C24" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="D24" t="str">
+        <v>题[q12] == 1 或 题[q15] == 1</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F24" t="str">
+        <v>绘画筛查命中被压垮/毁灭感信号，情绪风险高</v>
+      </c>
+      <c r="G24" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_EV_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>CS_AT_15</v>
+      </c>
+      <c r="C25" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>维度[CS_S1D5] &lt;= 3.5</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2</v>
+      </c>
+      <c r="F25" t="str">
+        <v>情感系统待建设，边缘学生连接通道不足</v>
+      </c>
+      <c r="G25" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_EV_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>CS_AT_15</v>
+      </c>
+      <c r="C26" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="D26" t="str">
+        <v>维度[CS_S3D1] &lt;= 3</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>学生版情感维度偏低，被接纳感与归属感不足</v>
+      </c>
+      <c r="G26" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1201,19 +1650,19 @@
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>CS_S1</v>
+        <v>CS_S6</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>题[q1] == 1 或 题[q2] == 1</v>
       </c>
       <c r="F2" t="str">
         <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>危机干预</v>
+        <v>安全危机·立即上报</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
@@ -1222,25 +1671,25 @@
         <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>班级系统整体处于危机水平，需立即干预</v>
+        <v>A/B级点检命中，须立即启动安全流程</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>A级（安全事件）出现自伤工具持有、攻击性威胁言论、躯体化反应</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>年级组长、心理专员、学校危机响应组</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>上报后48小时复核</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>CS_RX_25;CS_RX_28</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>立即按A-E响应SOP分级处置；现场使用情绪急救三步法稳住局面</v>
       </c>
       <c r="P2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="3">
@@ -1257,13 +1706,13 @@
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &lt;= 2 或 维度[CS_S1D1] &lt;= 2</v>
       </c>
       <c r="F3" t="str">
         <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>秩序奠基</v>
+        <v>秩序奠基期</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1272,25 +1721,25 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>年级组长、心理专员</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>介入后2周复评</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>CS_RX_01;CS_RX_02</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>启动五系统诊断向导定位短板；用堰塞湖破局法疏解积压问题</v>
       </c>
       <c r="P3" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="4">
@@ -1307,13 +1756,13 @@
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>均分 &lt;= 3.6 或 维度[CS_S1D1] &lt;= 3.5</v>
       </c>
       <c r="F4" t="str">
         <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>关系激活</v>
+        <v>关系激活期</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1322,7 +1771,7 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -1331,16 +1780,16 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>4周后复评</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>CS_RX_01;CS_RX_18</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>按短板系统匹配对应模块工具</v>
       </c>
       <c r="P4" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="5">
@@ -1351,19 +1800,19 @@
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>CS_S1</v>
+        <v>CS_S2</v>
       </c>
       <c r="D5" t="str">
         <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &lt;= 3.5 或 维度[CS_S2D1] &lt;= 3.5</v>
       </c>
       <c r="F5" t="str">
         <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>制度自转</v>
+        <v>制度自转期</v>
       </c>
       <c r="H5" t="str">
         <v>low</v>
@@ -1372,7 +1821,7 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -1381,16 +1830,16 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>4周后复评</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>CS_RX_01;CS_RX_09</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>按能量短板维度匹配专项工具</v>
       </c>
       <c r="P5" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="6">
@@ -1401,7 +1850,7 @@
         <v>class_system</v>
       </c>
       <c r="C6" t="str">
-        <v>CS_S2</v>
+        <v>CS_S3</v>
       </c>
       <c r="D6" t="str">
         <v>501</v>
@@ -1413,7 +1862,7 @@
         <v>orange</v>
       </c>
       <c r="G6" t="str">
-        <v>秩序奠基</v>
+        <v>秩序奠基期</v>
       </c>
       <c r="H6" t="str">
         <v>high</v>
@@ -1422,7 +1871,7 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -1440,7 +1889,7 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="7">
@@ -1451,7 +1900,7 @@
         <v>class_system</v>
       </c>
       <c r="C7" t="str">
-        <v>CS_S2</v>
+        <v>CS_S3</v>
       </c>
       <c r="D7" t="str">
         <v>502</v>
@@ -1463,7 +1912,7 @@
         <v>yellow</v>
       </c>
       <c r="G7" t="str">
-        <v>关系激活</v>
+        <v>关系激活期</v>
       </c>
       <c r="H7" t="str">
         <v>medium</v>
@@ -1472,7 +1921,7 @@
         <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -1490,7 +1939,7 @@
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="8">
@@ -1501,7 +1950,7 @@
         <v>class_system</v>
       </c>
       <c r="C8" t="str">
-        <v>CS_S2</v>
+        <v>CS_S3</v>
       </c>
       <c r="D8" t="str">
         <v>503</v>
@@ -1513,7 +1962,7 @@
         <v>blue</v>
       </c>
       <c r="G8" t="str">
-        <v>制度自转</v>
+        <v>制度自转期</v>
       </c>
       <c r="H8" t="str">
         <v>low</v>
@@ -1522,7 +1971,7 @@
         <v>否</v>
       </c>
       <c r="J8" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -1540,7 +1989,7 @@
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="9">
@@ -1551,7 +2000,7 @@
         <v>class_system</v>
       </c>
       <c r="C9" t="str">
-        <v>CS_S3</v>
+        <v>CS_S4</v>
       </c>
       <c r="D9" t="str">
         <v>504</v>
@@ -1563,7 +2012,7 @@
         <v>orange</v>
       </c>
       <c r="G9" t="str">
-        <v>秩序奠基</v>
+        <v>秩序奠基期</v>
       </c>
       <c r="H9" t="str">
         <v>high</v>
@@ -1572,7 +2021,7 @@
         <v>否</v>
       </c>
       <c r="J9" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1590,7 +2039,7 @@
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="10">
@@ -1601,7 +2050,7 @@
         <v>class_system</v>
       </c>
       <c r="C10" t="str">
-        <v>CS_S3</v>
+        <v>CS_S4</v>
       </c>
       <c r="D10" t="str">
         <v>505</v>
@@ -1613,7 +2062,7 @@
         <v>yellow</v>
       </c>
       <c r="G10" t="str">
-        <v>关系激活</v>
+        <v>关系激活期</v>
       </c>
       <c r="H10" t="str">
         <v>medium</v>
@@ -1622,7 +2071,7 @@
         <v>否</v>
       </c>
       <c r="J10" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1640,7 +2089,7 @@
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="11">
@@ -1651,7 +2100,7 @@
         <v>class_system</v>
       </c>
       <c r="C11" t="str">
-        <v>CS_S3</v>
+        <v>CS_S4</v>
       </c>
       <c r="D11" t="str">
         <v>506</v>
@@ -1663,7 +2112,7 @@
         <v>blue</v>
       </c>
       <c r="G11" t="str">
-        <v>制度自转</v>
+        <v>制度自转期</v>
       </c>
       <c r="H11" t="str">
         <v>low</v>
@@ -1672,7 +2121,7 @@
         <v>否</v>
       </c>
       <c r="J11" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -1690,7 +2139,7 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="12">
@@ -1701,7 +2150,7 @@
         <v>class_system</v>
       </c>
       <c r="C12" t="str">
-        <v>CS_S4</v>
+        <v>CS_S5</v>
       </c>
       <c r="D12" t="str">
         <v>507</v>
@@ -1713,7 +2162,7 @@
         <v>orange</v>
       </c>
       <c r="G12" t="str">
-        <v>秩序奠基</v>
+        <v>秩序奠基期</v>
       </c>
       <c r="H12" t="str">
         <v>high</v>
@@ -1722,7 +2171,7 @@
         <v>否</v>
       </c>
       <c r="J12" t="str">
-        <v>均分 ≥ 4 分：班级系统信号弱，处于秩序奠基期</v>
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -1740,7 +2189,7 @@
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="13">
@@ -1751,7 +2200,7 @@
         <v>class_system</v>
       </c>
       <c r="C13" t="str">
-        <v>CS_S4</v>
+        <v>CS_S5</v>
       </c>
       <c r="D13" t="str">
         <v>508</v>
@@ -1763,7 +2212,7 @@
         <v>yellow</v>
       </c>
       <c r="G13" t="str">
-        <v>关系激活</v>
+        <v>关系激活期</v>
       </c>
       <c r="H13" t="str">
         <v>medium</v>
@@ -1772,7 +2221,7 @@
         <v>否</v>
       </c>
       <c r="J13" t="str">
-        <v>均分 ≥ 3.5 分：班级处于关系激活期</v>
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1790,7 +2239,7 @@
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="14">
@@ -1801,7 +2250,7 @@
         <v>class_system</v>
       </c>
       <c r="C14" t="str">
-        <v>CS_S4</v>
+        <v>CS_S5</v>
       </c>
       <c r="D14" t="str">
         <v>509</v>
@@ -1813,7 +2262,7 @@
         <v>blue</v>
       </c>
       <c r="G14" t="str">
-        <v>制度自转</v>
+        <v>制度自转期</v>
       </c>
       <c r="H14" t="str">
         <v>low</v>
@@ -1822,7 +2271,7 @@
         <v>否</v>
       </c>
       <c r="J14" t="str">
-        <v>均分 ≥ 3 分：班级处于制度自转期</v>
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -1840,62 +2289,812 @@
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CS_GR_DEFAULT</v>
+        <v>CS_GR_AUTO_10</v>
       </c>
       <c r="B15" t="str">
         <v>class_system</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>CS_S6</v>
       </c>
       <c r="D15" t="str">
-        <v>999</v>
+        <v>510</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F15" t="str">
-        <v>green</v>
+        <v>orange</v>
       </c>
       <c r="G15" t="str">
-        <v>文化引领</v>
+        <v>秩序奠基期</v>
       </c>
       <c r="H15" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="I15" t="str">
         <v>否</v>
       </c>
       <c r="J15" t="str">
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_GR_AUTO_11</v>
+      </c>
+      <c r="B16" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C16" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>511</v>
+      </c>
+      <c r="E16" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G16" t="str">
+        <v>关系激活期</v>
+      </c>
+      <c r="H16" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I16" t="str">
+        <v>否</v>
+      </c>
+      <c r="J16" t="str">
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_GR_AUTO_12</v>
+      </c>
+      <c r="B17" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C17" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>512</v>
+      </c>
+      <c r="E17" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F17" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G17" t="str">
+        <v>制度自转期</v>
+      </c>
+      <c r="H17" t="str">
+        <v>low</v>
+      </c>
+      <c r="I17" t="str">
+        <v>否</v>
+      </c>
+      <c r="J17" t="str">
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_GR_AUTO_13</v>
+      </c>
+      <c r="B18" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C18" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="D18" t="str">
+        <v>513</v>
+      </c>
+      <c r="E18" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F18" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G18" t="str">
+        <v>秩序奠基期</v>
+      </c>
+      <c r="H18" t="str">
+        <v>high</v>
+      </c>
+      <c r="I18" t="str">
+        <v>否</v>
+      </c>
+      <c r="J18" t="str">
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_GR_AUTO_14</v>
+      </c>
+      <c r="B19" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C19" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="D19" t="str">
+        <v>514</v>
+      </c>
+      <c r="E19" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F19" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G19" t="str">
+        <v>关系激活期</v>
+      </c>
+      <c r="H19" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I19" t="str">
+        <v>否</v>
+      </c>
+      <c r="J19" t="str">
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_GR_AUTO_15</v>
+      </c>
+      <c r="B20" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C20" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>515</v>
+      </c>
+      <c r="E20" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F20" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G20" t="str">
+        <v>制度自转期</v>
+      </c>
+      <c r="H20" t="str">
+        <v>low</v>
+      </c>
+      <c r="I20" t="str">
+        <v>否</v>
+      </c>
+      <c r="J20" t="str">
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_GR_AUTO_16</v>
+      </c>
+      <c r="B21" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C21" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="D21" t="str">
+        <v>516</v>
+      </c>
+      <c r="E21" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F21" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G21" t="str">
+        <v>秩序奠基期</v>
+      </c>
+      <c r="H21" t="str">
+        <v>high</v>
+      </c>
+      <c r="I21" t="str">
+        <v>否</v>
+      </c>
+      <c r="J21" t="str">
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_GR_AUTO_17</v>
+      </c>
+      <c r="B22" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C22" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="D22" t="str">
+        <v>517</v>
+      </c>
+      <c r="E22" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F22" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G22" t="str">
+        <v>关系激活期</v>
+      </c>
+      <c r="H22" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I22" t="str">
+        <v>否</v>
+      </c>
+      <c r="J22" t="str">
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_GR_AUTO_18</v>
+      </c>
+      <c r="B23" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C23" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="D23" t="str">
+        <v>518</v>
+      </c>
+      <c r="E23" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F23" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G23" t="str">
+        <v>制度自转期</v>
+      </c>
+      <c r="H23" t="str">
+        <v>low</v>
+      </c>
+      <c r="I23" t="str">
+        <v>否</v>
+      </c>
+      <c r="J23" t="str">
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_GR_AUTO_19</v>
+      </c>
+      <c r="B24" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C24" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="D24" t="str">
+        <v>519</v>
+      </c>
+      <c r="E24" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F24" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G24" t="str">
+        <v>秩序奠基期</v>
+      </c>
+      <c r="H24" t="str">
+        <v>high</v>
+      </c>
+      <c r="I24" t="str">
+        <v>否</v>
+      </c>
+      <c r="J24" t="str">
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_GR_AUTO_20</v>
+      </c>
+      <c r="B25" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C25" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="D25" t="str">
+        <v>520</v>
+      </c>
+      <c r="E25" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F25" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G25" t="str">
+        <v>关系激活期</v>
+      </c>
+      <c r="H25" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I25" t="str">
+        <v>否</v>
+      </c>
+      <c r="J25" t="str">
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_GR_AUTO_21</v>
+      </c>
+      <c r="B26" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C26" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="D26" t="str">
+        <v>521</v>
+      </c>
+      <c r="E26" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F26" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G26" t="str">
+        <v>制度自转期</v>
+      </c>
+      <c r="H26" t="str">
+        <v>low</v>
+      </c>
+      <c r="I26" t="str">
+        <v>否</v>
+      </c>
+      <c r="J26" t="str">
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CS_GR_AUTO_22</v>
+      </c>
+      <c r="B27" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C27" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="D27" t="str">
+        <v>522</v>
+      </c>
+      <c r="E27" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F27" t="str">
+        <v>orange</v>
+      </c>
+      <c r="G27" t="str">
+        <v>秩序奠基期</v>
+      </c>
+      <c r="H27" t="str">
+        <v>high</v>
+      </c>
+      <c r="I27" t="str">
+        <v>否</v>
+      </c>
+      <c r="J27" t="str">
+        <v>总分&lt;30：立即介入，学校支援，必要时拆班/转介</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_GR_AUTO_23</v>
+      </c>
+      <c r="B28" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C28" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="D28" t="str">
+        <v>523</v>
+      </c>
+      <c r="E28" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F28" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G28" t="str">
+        <v>关系激活期</v>
+      </c>
+      <c r="H28" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I28" t="str">
+        <v>否</v>
+      </c>
+      <c r="J28" t="str">
+        <v>总分30-59：系统性问题或待建设弱项，启动重建+4周专项</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_GR_AUTO_24</v>
+      </c>
+      <c r="B29" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C29" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="D29" t="str">
+        <v>524</v>
+      </c>
+      <c r="E29" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F29" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G29" t="str">
+        <v>制度自转期</v>
+      </c>
+      <c r="H29" t="str">
+        <v>low</v>
+      </c>
+      <c r="I29" t="str">
+        <v>否</v>
+      </c>
+      <c r="J29" t="str">
+        <v>能量场均分≤3.5：班级能量偏低，安排4周专项观察与建设</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_GR_DEFAULT</v>
+      </c>
+      <c r="B30" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>999</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>green</v>
+      </c>
+      <c r="G30" t="str">
+        <v>文化生成期</v>
+      </c>
+      <c r="H30" t="str">
+        <v>low</v>
+      </c>
+      <c r="I30" t="str">
+        <v>否</v>
+      </c>
+      <c r="J30" t="str">
         <v>本次评估未发现需要重点干预的信号</v>
       </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v>班级系统建设手册v1</v>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1941,31 +3140,31 @@
         <v>class_system</v>
       </c>
       <c r="B2" t="str">
-        <v>量表[CS_S1].均分 &gt;= 4</v>
+        <v>量表[CS_S6].题[q1] == 1 或 量表[CS_S6].题[q2] == 1</v>
       </c>
       <c r="C2" t="str">
-        <v>班级系统整体处于危机水平，需立即干预</v>
+        <v>A/B级点检命中，须立即启动安全流程</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>联系年级组长与心理专员，暂停非必要活动</v>
+        <v>24-48小时内上报学校并通知心理专员，A级同步公安/医疗转介</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出；提示转入学生个体问题模块；通知年级组长；记录安全事件</v>
+        <v>停止常规建议输出；A/B级24-48小时内上报学校并通知心理专员；A级同步公安/医疗转介；记录安全事件</v>
       </c>
       <c r="G2" t="str">
-        <v>完成全班关系筛查且年级组长确认无欺凌情形</v>
+        <v>学校心理专业评估确认风险解除后</v>
       </c>
       <c r="H2" t="str">
-        <v>年级组长</v>
+        <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在班级系统评估中触发红线，请尽快登录系统查看处置要求。</v>
+        <v>[教师姓名]老师触发了心理风险红线（A/B级点检命中），请尽快登录系统查看处置要求。</v>
       </c>
       <c r="J2" t="str">
-        <v>班级系统建设手册v1</v>
+        <v>班级系统建设 2.0 三库文档（2026-07-27 版）</v>
       </c>
     </row>
   </sheetData>
